--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eaton-my.sharepoint.com/personal/arelycastillo_eaton_com/Documents/Documents/Python/orden_cpdi/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/098a8ea1b880659c/Documents/GitHub/Eaton/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3505" documentId="8_{CFB2FA99-D5D7-426D-AC7E-F32E00CE30D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3CBA567-CFC4-4CD9-A4DD-EBCAFB7D5DF1}"/>
+  <xr:revisionPtr revIDLastSave="3506" documentId="8_{CFB2FA99-D5D7-426D-AC7E-F32E00CE30D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67DCC8F6-B4D8-49E7-934A-E38C42E19C87}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="11" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="3" activeTab="4" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista" sheetId="1" r:id="rId1"/>
@@ -2568,6 +2568,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2888,19 +2892,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C460FD-853F-48A8-BB18-DB58CBD5BD31}">
   <dimension ref="A1:U102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
-    <col min="6" max="11" width="23.5703125" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" customWidth="1"/>
-    <col min="13" max="18" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="6" max="11" width="23.5546875" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="13" max="18" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2956,7 +2960,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2974,7 +2978,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3009,7 +3013,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3044,7 +3048,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3082,7 +3086,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3155,7 +3159,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3190,7 +3194,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3225,7 +3229,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3260,7 +3264,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -3295,7 +3299,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3330,7 +3334,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -3365,7 +3369,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3415,7 +3419,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3468,7 +3472,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -3518,7 +3522,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3568,7 +3572,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -3618,7 +3622,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -3668,7 +3672,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -3718,7 +3722,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -3768,7 +3772,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -3818,7 +3822,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -3868,7 +3872,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -3918,7 +3922,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -3968,7 +3972,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -4018,7 +4022,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -4059,7 +4063,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -4100,7 +4104,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -4141,7 +4145,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -4182,7 +4186,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -4223,7 +4227,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -4264,7 +4268,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -4281,7 +4285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -4316,7 +4320,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -4351,7 +4355,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -4386,7 +4390,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -4421,7 +4425,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -4456,7 +4460,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -4491,7 +4495,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -4526,7 +4530,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -4561,7 +4565,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -4596,7 +4600,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -4613,7 +4617,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -4648,7 +4652,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -4683,7 +4687,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -4718,7 +4722,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -4753,7 +4757,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -4788,7 +4792,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -4823,7 +4827,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -4858,7 +4862,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>81</v>
       </c>
@@ -4893,7 +4897,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>101</v>
       </c>
@@ -4963,7 +4967,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -4998,7 +5002,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -5033,7 +5037,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -5068,7 +5072,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -5103,7 +5107,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>109</v>
       </c>
@@ -5138,7 +5142,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -5179,7 +5183,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -5220,7 +5224,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -5261,7 +5265,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -5302,7 +5306,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -5343,7 +5347,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -5384,7 +5388,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>123</v>
       </c>
@@ -5425,7 +5429,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>125</v>
       </c>
@@ -5466,7 +5470,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -5507,7 +5511,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -5548,7 +5552,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>131</v>
       </c>
@@ -5589,7 +5593,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>133</v>
       </c>
@@ -5630,7 +5634,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>135</v>
       </c>
@@ -5671,7 +5675,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>137</v>
       </c>
@@ -5712,7 +5716,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>139</v>
       </c>
@@ -5753,7 +5757,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>141</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>143</v>
       </c>
@@ -5835,7 +5839,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>145</v>
       </c>
@@ -5876,7 +5880,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>147</v>
       </c>
@@ -5917,7 +5921,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>149</v>
       </c>
@@ -5952,7 +5956,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>151</v>
       </c>
@@ -5987,7 +5991,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>153</v>
       </c>
@@ -6022,7 +6026,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -6057,7 +6061,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>157</v>
       </c>
@@ -6092,7 +6096,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -6127,7 +6131,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>161</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -6197,7 +6201,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -6267,7 +6271,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>169</v>
       </c>
@@ -6302,7 +6306,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>171</v>
       </c>
@@ -6337,7 +6341,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>173</v>
       </c>
@@ -6372,7 +6376,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>175</v>
       </c>
@@ -6407,7 +6411,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>177</v>
       </c>
@@ -6442,7 +6446,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>179</v>
       </c>
@@ -6477,7 +6481,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>181</v>
       </c>
@@ -6497,7 +6501,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>183</v>
       </c>
@@ -6517,7 +6521,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>185</v>
       </c>
@@ -6537,7 +6541,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>187</v>
       </c>
@@ -6560,7 +6564,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>189</v>
       </c>
@@ -6583,7 +6587,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>191</v>
       </c>
@@ -6606,7 +6610,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>193</v>
       </c>
@@ -6629,7 +6633,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>195</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -6685,15 +6689,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D487D21-F885-403B-A303-1EC36DC187C1}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6710,7 +6714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6727,7 +6731,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6744,7 +6748,7 @@
         <v>26073</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6761,7 +6765,7 @@
         <v>5969</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -6778,7 +6782,7 @@
         <v>16696</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -6795,7 +6799,7 @@
         <v>10644</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -6812,7 +6816,7 @@
         <v>5531</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -6829,7 +6833,7 @@
         <v>18546</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -6846,7 +6850,7 @@
         <v>20436</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -6872,19 +6876,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AD93CD-4665-42DC-AC4B-4CF05C73D8EA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6910,7 +6914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>158276</v>
       </c>
@@ -6936,7 +6940,7 @@
         <v>5256</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>158277</v>
       </c>
@@ -6962,7 +6966,7 @@
         <v>5256</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>158278</v>
       </c>
@@ -6988,7 +6992,7 @@
         <v>5256</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>158279</v>
       </c>
@@ -7014,7 +7018,7 @@
         <v>5256</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>158280</v>
       </c>
@@ -7040,7 +7044,7 @@
         <v>7377</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>158281</v>
       </c>
@@ -7066,7 +7070,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>158282</v>
       </c>
@@ -7092,7 +7096,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>158283</v>
       </c>
@@ -7118,7 +7122,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>158284</v>
       </c>
@@ -7144,7 +7148,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>158285</v>
       </c>
@@ -7170,7 +7174,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>158286</v>
       </c>
@@ -7196,7 +7200,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>158287</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>111554</v>
       </c>
@@ -7248,7 +7252,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>111557</v>
       </c>
@@ -7274,7 +7278,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>111560</v>
       </c>
@@ -7300,7 +7304,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>111563</v>
       </c>
@@ -7326,7 +7330,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>111566</v>
       </c>
@@ -7352,7 +7356,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>111569</v>
       </c>
@@ -7378,7 +7382,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>111572</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>111575</v>
       </c>
@@ -7430,7 +7434,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>111578</v>
       </c>
@@ -7456,7 +7460,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>112499</v>
       </c>
@@ -7482,7 +7486,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>111555</v>
       </c>
@@ -7508,7 +7512,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>111558</v>
       </c>
@@ -7534,7 +7538,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>111561</v>
       </c>
@@ -7560,7 +7564,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>111564</v>
       </c>
@@ -7586,7 +7590,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>111567</v>
       </c>
@@ -7612,7 +7616,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>111570</v>
       </c>
@@ -7638,7 +7642,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>111573</v>
       </c>
@@ -7664,7 +7668,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>111576</v>
       </c>
@@ -7690,7 +7694,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>111579</v>
       </c>
@@ -7716,7 +7720,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>131276</v>
       </c>
@@ -7742,7 +7746,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>131277</v>
       </c>
@@ -7768,7 +7772,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>131278</v>
       </c>
@@ -7794,7 +7798,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>131279</v>
       </c>
@@ -7820,7 +7824,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>131280</v>
       </c>
@@ -7846,7 +7850,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>131281</v>
       </c>
@@ -7872,7 +7876,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>119735</v>
       </c>
@@ -7898,7 +7902,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>116973</v>
       </c>
@@ -7924,7 +7928,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>116974</v>
       </c>
@@ -7950,7 +7954,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>116975</v>
       </c>
@@ -7976,7 +7980,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>131668</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>121804</v>
       </c>
@@ -8028,7 +8032,7 @@
         <v>4611</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>121805</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>4611</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>121806</v>
       </c>
@@ -8080,7 +8084,7 @@
         <v>4611</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>121807</v>
       </c>
@@ -8123,18 +8127,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC118DC-A31E-40E5-8016-5940C6148308}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -8163,7 +8167,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>306</v>
       </c>
@@ -8192,7 +8196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>307</v>
       </c>
@@ -8221,7 +8225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>308</v>
       </c>
@@ -8250,7 +8254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>309</v>
       </c>
@@ -8279,7 +8283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>310</v>
       </c>
@@ -8308,7 +8312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>311</v>
       </c>
@@ -8337,7 +8341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>312</v>
       </c>
@@ -8366,7 +8370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>313</v>
       </c>
@@ -8395,7 +8399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>314</v>
       </c>
@@ -8424,7 +8428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -8453,7 +8457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>316</v>
       </c>
@@ -8482,7 +8486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>317</v>
       </c>
@@ -8511,7 +8515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>318</v>
       </c>
@@ -8540,7 +8544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>334</v>
       </c>
@@ -8569,7 +8573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>335</v>
       </c>
@@ -8598,7 +8602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>336</v>
       </c>
@@ -8627,7 +8631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>337</v>
       </c>
@@ -8656,7 +8660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>338</v>
       </c>
@@ -8685,7 +8689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>344</v>
       </c>
@@ -8714,7 +8718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>345</v>
       </c>
@@ -8743,7 +8747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>346</v>
       </c>
@@ -8772,7 +8776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>350</v>
       </c>
@@ -8801,7 +8805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>351</v>
       </c>
@@ -8830,7 +8834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>354</v>
       </c>
@@ -8859,7 +8863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>355</v>
       </c>
@@ -8888,7 +8892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>356</v>
       </c>
@@ -8917,7 +8921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>360</v>
       </c>
@@ -8946,7 +8950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>362</v>
       </c>
@@ -8975,7 +8979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>363</v>
       </c>
@@ -9004,7 +9008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>366</v>
       </c>
@@ -9033,7 +9037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>367</v>
       </c>
@@ -9062,7 +9066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>369</v>
       </c>
@@ -9091,7 +9095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>371</v>
       </c>
@@ -9120,7 +9124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>372</v>
       </c>
@@ -9149,7 +9153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>373</v>
       </c>
@@ -9178,7 +9182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>376</v>
       </c>
@@ -9207,7 +9211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>377</v>
       </c>
@@ -9236,7 +9240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>380</v>
       </c>
@@ -9265,7 +9269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>381</v>
       </c>
@@ -9294,7 +9298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>382</v>
       </c>
@@ -9323,7 +9327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>386</v>
       </c>
@@ -9352,7 +9356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>390</v>
       </c>
@@ -9381,7 +9385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>391</v>
       </c>
@@ -9410,7 +9414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>392</v>
       </c>
@@ -9439,7 +9443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>393</v>
       </c>
@@ -9468,7 +9472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>394</v>
       </c>
@@ -9497,7 +9501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>395</v>
       </c>
@@ -9526,7 +9530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>396</v>
       </c>
@@ -9555,7 +9559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>397</v>
       </c>
@@ -9584,7 +9588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>398</v>
       </c>
@@ -9613,7 +9617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>409</v>
       </c>
@@ -9642,7 +9646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>410</v>
       </c>
@@ -9671,7 +9675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>411</v>
       </c>
@@ -9700,7 +9704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>415</v>
       </c>
@@ -9729,7 +9733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>416</v>
       </c>
@@ -9758,7 +9762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>417</v>
       </c>
@@ -9787,7 +9791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>421</v>
       </c>
@@ -9816,7 +9820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>422</v>
       </c>
@@ -9845,7 +9849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>425</v>
       </c>
@@ -9874,7 +9878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>427</v>
       </c>
@@ -9903,7 +9907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>429</v>
       </c>
@@ -9932,7 +9936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>431</v>
       </c>
@@ -9961,7 +9965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>433</v>
       </c>
@@ -9990,7 +9994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>435</v>
       </c>
@@ -10019,7 +10023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>437</v>
       </c>
@@ -10048,7 +10052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>439</v>
       </c>
@@ -10077,7 +10081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>441</v>
       </c>
@@ -10106,7 +10110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>443</v>
       </c>
@@ -10135,7 +10139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>445</v>
       </c>
@@ -10164,7 +10168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>446</v>
       </c>
@@ -10193,7 +10197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>449</v>
       </c>
@@ -10222,7 +10226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>451</v>
       </c>
@@ -10251,7 +10255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>452</v>
       </c>
@@ -10280,7 +10284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>455</v>
       </c>
@@ -10309,7 +10313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>779</v>
       </c>
@@ -10338,7 +10342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>781</v>
       </c>
@@ -10367,7 +10371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>783</v>
       </c>
@@ -10396,7 +10400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>785</v>
       </c>
@@ -10441,9 +10445,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35D01AB-AD7C-4FA0-A1EC-067E5208E301}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10459,14 +10463,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75CEA00-E98C-48D1-8951-FCFD66D8871D}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10486,7 +10490,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>644</v>
       </c>
@@ -10506,7 +10510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>646</v>
       </c>
@@ -10526,7 +10530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>648</v>
       </c>
@@ -10546,7 +10550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>650</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>652</v>
       </c>
@@ -10586,7 +10590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>653</v>
       </c>
@@ -10606,7 +10610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>654</v>
       </c>
@@ -10626,7 +10630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>656</v>
       </c>
@@ -10646,7 +10650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>658</v>
       </c>
@@ -10666,7 +10670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>660</v>
       </c>
@@ -10686,7 +10690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>662</v>
       </c>
@@ -10706,7 +10710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>663</v>
       </c>
@@ -10726,7 +10730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>664</v>
       </c>
@@ -10746,7 +10750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>666</v>
       </c>
@@ -10766,7 +10770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>668</v>
       </c>
@@ -10786,7 +10790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>670</v>
       </c>
@@ -10815,20 +10819,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7291FE-1C80-46D5-A44B-ECDC4D68CA2E}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10866,7 +10870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -10904,7 +10908,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -10942,7 +10946,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -10980,7 +10984,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -11018,7 +11022,7 @@
         <v>3347</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -11056,7 +11060,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -11094,7 +11098,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -11132,7 +11136,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -11170,7 +11174,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -11208,7 +11212,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -11246,7 +11250,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -11284,7 +11288,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -11322,7 +11326,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -11360,7 +11364,7 @@
         <v>3763</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -11398,7 +11402,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -11436,7 +11440,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -11474,7 +11478,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -11512,7 +11516,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>121</v>
       </c>
@@ -11550,7 +11554,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>123</v>
       </c>
@@ -11588,7 +11592,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -11626,7 +11630,7 @@
         <v>9432</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -11664,7 +11668,7 @@
         <v>6129</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -11702,7 +11706,7 @@
         <v>8433</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -11740,7 +11744,7 @@
         <v>8543</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -11778,7 +11782,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -11816,7 +11820,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -11854,7 +11858,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>141</v>
       </c>
@@ -11892,7 +11896,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -11930,7 +11934,7 @@
         <v>3478</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -11968,7 +11972,7 @@
         <v>4009</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -12006,7 +12010,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -12044,7 +12048,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -12082,7 +12086,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -12120,7 +12124,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -12158,7 +12162,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -12196,7 +12200,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -12234,7 +12238,7 @@
         <v>9432</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -12272,7 +12276,7 @@
         <v>6129</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -12310,7 +12314,7 @@
         <v>8433</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -12348,7 +12352,7 @@
         <v>8543</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -12386,7 +12390,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -12424,7 +12428,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>137</v>
       </c>
@@ -12462,7 +12466,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -12500,7 +12504,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>143</v>
       </c>
@@ -12538,7 +12542,7 @@
         <v>3478</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -12576,7 +12580,7 @@
         <v>4009</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -12614,7 +12618,7 @@
         <v>3347</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -12652,7 +12656,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -12690,7 +12694,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>129</v>
       </c>
@@ -12728,7 +12732,7 @@
         <v>8433</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -12766,7 +12770,7 @@
         <v>8433</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -12804,7 +12808,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -12842,7 +12846,7 @@
         <v>3763</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>145</v>
       </c>
@@ -12884,7 +12888,7 @@
   <autoFilter ref="A1:L54" xr:uid="{4F7291FE-1C80-46D5-A44B-ECDC4D68CA2E}">
     <filterColumn colId="4">
       <filters>
-        <filter val="PDG"/>
+        <filter val="BZM"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -12896,14 +12900,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E191415-7327-4CFF-B229-D7F54ABBDB32}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -12917,7 +12921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>185</v>
       </c>
@@ -12939,14 +12943,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25522428-B4D4-43A2-8ABC-2052B8318014}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -12960,7 +12964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>183</v>
       </c>
@@ -12982,15 +12986,15 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A5EDD5-EC5E-4B4D-BAE8-EF24A4D32E1E}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -13004,7 +13008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>181</v>
       </c>
@@ -13027,15 +13031,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="57.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="57.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -13058,7 +13062,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>464</v>
       </c>
@@ -13081,7 +13085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>466</v>
       </c>
@@ -13104,7 +13108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>468</v>
       </c>
@@ -13127,7 +13131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>469</v>
       </c>
@@ -13150,7 +13154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>470</v>
       </c>
@@ -13173,7 +13177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>471</v>
       </c>
@@ -13196,7 +13200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>472</v>
       </c>
@@ -13219,7 +13223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>473</v>
       </c>
@@ -13242,7 +13246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>474</v>
       </c>
@@ -13265,7 +13269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>475</v>
       </c>
@@ -13288,7 +13292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>484</v>
       </c>
@@ -13311,7 +13315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>485</v>
       </c>
@@ -13334,7 +13338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>486</v>
       </c>
@@ -13357,7 +13361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>487</v>
       </c>
@@ -13380,7 +13384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>488</v>
       </c>
@@ -13403,7 +13407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>489</v>
       </c>
@@ -13426,7 +13430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>496</v>
       </c>
@@ -13449,7 +13453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>498</v>
       </c>
@@ -13472,7 +13476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>500</v>
       </c>
@@ -13495,7 +13499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>502</v>
       </c>
@@ -13518,7 +13522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>503</v>
       </c>
@@ -13541,7 +13545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>506</v>
       </c>
@@ -13564,7 +13568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>507</v>
       </c>
@@ -13587,7 +13591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>508</v>
       </c>
@@ -13610,7 +13614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>512</v>
       </c>
@@ -13633,7 +13637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>514</v>
       </c>
@@ -13656,7 +13660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>516</v>
       </c>
@@ -13679,7 +13683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>518</v>
       </c>
@@ -13702,7 +13706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>519</v>
       </c>
@@ -13725,7 +13729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>522</v>
       </c>
@@ -13748,7 +13752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>524</v>
       </c>
@@ -13771,7 +13775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>526</v>
       </c>
@@ -13794,7 +13798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>527</v>
       </c>
@@ -13817,7 +13821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>530</v>
       </c>
@@ -13840,7 +13844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>532</v>
       </c>
@@ -13863,7 +13867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>533</v>
       </c>
@@ -13886,7 +13890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>534</v>
       </c>
@@ -13909,7 +13913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>535</v>
       </c>
@@ -13932,7 +13936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>536</v>
       </c>
@@ -13955,7 +13959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>537</v>
       </c>
@@ -13978,7 +13982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>538</v>
       </c>
@@ -14001,7 +14005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>546</v>
       </c>
@@ -14024,7 +14028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>548</v>
       </c>
@@ -14047,7 +14051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>550</v>
       </c>
@@ -14070,7 +14074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>552</v>
       </c>
@@ -14093,7 +14097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>554</v>
       </c>
@@ -14116,7 +14120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>555</v>
       </c>
@@ -14139,7 +14143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>556</v>
       </c>
@@ -14162,7 +14166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>557</v>
       </c>
@@ -14185,7 +14189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>558</v>
       </c>
@@ -14208,7 +14212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>564</v>
       </c>
@@ -14231,7 +14235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>565</v>
       </c>
@@ -14254,7 +14258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>568</v>
       </c>
@@ -14277,7 +14281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>570</v>
       </c>
@@ -14300,7 +14304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>571</v>
       </c>
@@ -14323,7 +14327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>572</v>
       </c>
@@ -14346,7 +14350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>574</v>
       </c>
@@ -14369,7 +14373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>576</v>
       </c>
@@ -14392,7 +14396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>578</v>
       </c>
@@ -14415,7 +14419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>580</v>
       </c>
@@ -14438,7 +14442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>582</v>
       </c>
@@ -14461,7 +14465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>583</v>
       </c>
@@ -14484,7 +14488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>584</v>
       </c>
@@ -14507,7 +14511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>585</v>
       </c>
@@ -14530,7 +14534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>590</v>
       </c>
@@ -14553,7 +14557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>592</v>
       </c>
@@ -14576,7 +14580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>594</v>
       </c>
@@ -14599,7 +14603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>596</v>
       </c>
@@ -14622,7 +14626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>597</v>
       </c>
@@ -14645,7 +14649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>598</v>
       </c>
@@ -14668,7 +14672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>599</v>
       </c>
@@ -14691,7 +14695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>602</v>
       </c>
@@ -14714,7 +14718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>603</v>
       </c>
@@ -14737,7 +14741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>604</v>
       </c>
@@ -14760,7 +14764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>605</v>
       </c>
@@ -14783,7 +14787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>606</v>
       </c>
@@ -14806,7 +14810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>612</v>
       </c>
@@ -14829,7 +14833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>614</v>
       </c>
@@ -14852,7 +14856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>615</v>
       </c>
@@ -14875,7 +14879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>616</v>
       </c>
@@ -14898,7 +14902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>620</v>
       </c>
@@ -14921,7 +14925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>622</v>
       </c>
@@ -14944,7 +14948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>624</v>
       </c>
@@ -14967,7 +14971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>626</v>
       </c>
@@ -14990,7 +14994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>628</v>
       </c>
@@ -15013,7 +15017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>630</v>
       </c>
@@ -15036,7 +15040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>632</v>
       </c>
@@ -15059,7 +15063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>634</v>
       </c>
@@ -15082,7 +15086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>636</v>
       </c>
@@ -15105,7 +15109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>638</v>
       </c>
@@ -15128,7 +15132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>639</v>
       </c>
@@ -15151,7 +15155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>640</v>
       </c>
@@ -15190,14 +15194,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7A467A-8250-4705-9EA7-960D198EF57F}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15217,7 +15221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -15234,7 +15238,7 @@
         <v>131929</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -15251,7 +15255,7 @@
         <v>110044</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -15268,7 +15272,7 @@
         <v>205776</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -15288,7 +15292,7 @@
         <v>31109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>189</v>
       </c>
@@ -15308,7 +15312,7 @@
         <v>37170</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>191</v>
       </c>
@@ -15328,7 +15332,7 @@
         <v>42146</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -15348,7 +15352,7 @@
         <v>51982</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>195</v>
       </c>
@@ -15368,7 +15372,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -15396,15 +15400,15 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE280E8-1030-4D15-BB87-39545B71D8FE}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15421,7 +15425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -15438,7 +15442,7 @@
         <v>110044</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -15463,15 +15467,15 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC3D159-7610-47A2-B6E6-4BC8DBFBC056}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15491,7 +15495,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>672</v>
       </c>
@@ -15511,7 +15515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>674</v>
       </c>
@@ -15531,7 +15535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>676</v>
       </c>
@@ -15551,7 +15555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>678</v>
       </c>
@@ -15571,7 +15575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>680</v>
       </c>
@@ -15591,7 +15595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>682</v>
       </c>
@@ -15611,7 +15615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>684</v>
       </c>
@@ -15631,7 +15635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>686</v>
       </c>
@@ -15651,7 +15655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>688</v>
       </c>
@@ -15671,7 +15675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>690</v>
       </c>
@@ -15691,7 +15695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>692</v>
       </c>
@@ -15711,7 +15715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>694</v>
       </c>
@@ -15731,7 +15735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>696</v>
       </c>
@@ -15751,7 +15755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>698</v>
       </c>
@@ -15771,7 +15775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>699</v>
       </c>
@@ -15799,15 +15803,15 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D45C86-8F36-4726-BB8C-72524168E246}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15827,7 +15831,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>701</v>
       </c>
@@ -15847,7 +15851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>703</v>
       </c>
@@ -15867,7 +15871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>705</v>
       </c>
@@ -15887,7 +15891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>707</v>
       </c>
@@ -15907,7 +15911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>709</v>
       </c>
@@ -15927,7 +15931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>711</v>
       </c>
@@ -15947,7 +15951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>713</v>
       </c>
@@ -15967,7 +15971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>714</v>
       </c>
@@ -15987,7 +15991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>716</v>
       </c>
@@ -16016,17 +16020,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0952EC0-78E2-4227-94D1-113308784769}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -16049,7 +16053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -16072,7 +16076,7 @@
         <v>40487</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -16095,7 +16099,7 @@
         <v>9507</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -16118,7 +16122,7 @@
         <v>16041</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -16141,7 +16145,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -16164,7 +16168,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -16187,7 +16191,7 @@
         <v>110044</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -16218,15 +16222,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF069F-11F0-41FB-B939-51B5F45B8CB2}">
   <dimension ref="A1:E111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -16243,7 +16247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>729</v>
       </c>
@@ -16260,7 +16264,7 @@
         <v>103121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>730</v>
       </c>
@@ -16277,7 +16281,7 @@
         <v>118541</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>731</v>
       </c>
@@ -16294,7 +16298,7 @@
         <v>135356</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>732</v>
       </c>
@@ -16311,7 +16315,7 @@
         <v>128574</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>733</v>
       </c>
@@ -16328,7 +16332,7 @@
         <v>145962</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>734</v>
       </c>
@@ -16345,7 +16349,7 @@
         <v>163173</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>736</v>
       </c>
@@ -16362,7 +16366,7 @@
         <v>115840</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>737</v>
       </c>
@@ -16379,7 +16383,7 @@
         <v>131702</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>738</v>
       </c>
@@ -16396,7 +16400,7 @@
         <v>148391</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>739</v>
       </c>
@@ -16413,7 +16417,7 @@
         <v>141557</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>740</v>
       </c>
@@ -16430,7 +16434,7 @@
         <v>159273</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>741</v>
       </c>
@@ -16447,7 +16451,7 @@
         <v>178319</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>742</v>
       </c>
@@ -16464,583 +16468,583 @@
         <v>7067</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="11"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="11"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="11"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="11"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="11"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="11"/>
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="11"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="11"/>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="11"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="11"/>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="11"/>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="11"/>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="11"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="11"/>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="11"/>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="11"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="11"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="11"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="11"/>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="11"/>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="11"/>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="11"/>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="11"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="11"/>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="11"/>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="11"/>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="11"/>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="11"/>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="11"/>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="11"/>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="11"/>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="11"/>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="11"/>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
@@ -17054,16 +17058,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E21284-68D2-4B7C-8891-F33FB2D4174C}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17083,7 +17087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -17103,7 +17107,7 @@
         <v>23264</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -17123,7 +17127,7 @@
         <v>40773</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -17143,7 +17147,7 @@
         <v>22207</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -17163,7 +17167,7 @@
         <v>38919</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -17183,7 +17187,7 @@
         <v>3156</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -17211,14 +17215,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7C1833-5DC7-4038-9B0D-2D47C7DFB4A9}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17232,7 +17236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -17246,7 +17250,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -17268,16 +17272,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6578FDA-80BC-4521-8BA7-3C8BD0257781}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17297,7 +17301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -17317,7 +17321,7 @@
         <v>38919</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -17337,7 +17341,7 @@
         <v>61443</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -17357,7 +17361,7 @@
         <v>38919</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -17377,7 +17381,7 @@
         <v>58771</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -17397,7 +17401,7 @@
         <v>3156</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -17425,15 +17429,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC341ECE-6FE5-41E4-9F6E-2DB5B33BB710}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17450,7 +17454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -17467,7 +17471,7 @@
         <v>110044</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -17484,7 +17488,7 @@
         <v>15986</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -17501,7 +17505,7 @@
         <v>211304</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -17526,14 +17530,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB46B0E-37A5-4181-9C58-3C1127A0CA35}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17550,7 +17554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -17567,7 +17571,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -17584,7 +17588,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -17601,7 +17605,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -17618,7 +17622,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -17635,7 +17639,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -17652,7 +17656,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -17669,7 +17673,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -17686,7 +17690,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -17703,7 +17707,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>155</v>
       </c>
@@ -17720,7 +17724,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -17737,7 +17741,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>159</v>
       </c>
@@ -17754,7 +17758,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -17771,7 +17775,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -17788,7 +17792,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -17805,7 +17809,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -17822,7 +17826,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -17839,7 +17843,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -17856,7 +17860,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -17873,7 +17877,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -17890,7 +17894,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -17907,7 +17911,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -17924,7 +17928,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -17941,7 +17945,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -17958,7 +17962,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>149</v>
       </c>
@@ -17975,7 +17979,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>151</v>
       </c>
@@ -17992,7 +17996,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -18009,7 +18013,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>155</v>
       </c>
@@ -18026,7 +18030,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -18043,7 +18047,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>159</v>
       </c>
@@ -18060,7 +18064,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -18077,7 +18081,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>151</v>
       </c>
@@ -18094,7 +18098,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -18111,7 +18115,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -18128,7 +18132,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -18145,7 +18149,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>159</v>
       </c>

--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/098a8ea1b880659c/Documents/GitHub/Eaton/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eaton-my.sharepoint.com/personal/arelycastillo_eaton_com/Documents/Documents/GitHub/Eaton/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="221" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33750515-3870-4167-971B-F7306F2CBFE4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura" sheetId="9" r:id="rId1"/>
@@ -2520,10 +2520,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2844,15 +2840,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7A467A-8250-4705-9EA7-960D198EF57F}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2878,7 +2874,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2902,7 +2898,7 @@
         <v>0.53449999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -2926,7 +2922,7 @@
         <v>0.62250000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -2950,7 +2946,7 @@
         <v>0.57920000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -2977,7 +2973,7 @@
         <v>0.68020000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>173</v>
       </c>
@@ -3004,7 +3000,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>175</v>
       </c>
@@ -3031,7 +3027,7 @@
         <v>0.64359999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -3058,7 +3054,7 @@
         <v>0.66600000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>179</v>
       </c>
@@ -3085,7 +3081,7 @@
         <v>0.65149999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>181</v>
       </c>
@@ -3120,15 +3116,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB46B0E-37A5-4181-9C58-3C1127A0CA35}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3151,7 +3147,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -3175,7 +3171,7 @@
         <v>0.79630000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -3199,7 +3195,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -3223,7 +3219,7 @@
         <v>0.71460000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -3247,7 +3243,7 @@
         <v>0.60109999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -3271,7 +3267,7 @@
         <v>0.64329999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -3295,7 +3291,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -3319,7 +3315,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -3343,7 +3339,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -3367,7 +3363,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>155</v>
       </c>
@@ -3391,7 +3387,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -3415,7 +3411,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>159</v>
       </c>
@@ -3439,7 +3435,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -3463,7 +3459,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -3487,7 +3483,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -3511,7 +3507,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -3535,7 +3531,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -3559,7 +3555,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -3583,7 +3579,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -3607,7 +3603,7 @@
         <v>0.79630000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -3631,7 +3627,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -3655,7 +3651,7 @@
         <v>0.71460000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -3679,7 +3675,7 @@
         <v>0.60109999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -3703,7 +3699,7 @@
         <v>0.64329999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -3727,7 +3723,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>149</v>
       </c>
@@ -3751,7 +3747,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>151</v>
       </c>
@@ -3775,7 +3771,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -3799,7 +3795,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>155</v>
       </c>
@@ -3823,7 +3819,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -3847,7 +3843,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>159</v>
       </c>
@@ -3871,7 +3867,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -3895,7 +3891,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>151</v>
       </c>
@@ -3919,7 +3915,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -3943,7 +3939,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -3967,7 +3963,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -3991,7 +3987,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>159</v>
       </c>
@@ -4024,17 +4020,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D487D21-F885-403B-A303-1EC36DC187C1}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4057,7 +4053,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4081,7 +4077,7 @@
         <v>0.58479999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -4105,7 +4101,7 @@
         <v>0.52429999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4129,7 +4125,7 @@
         <v>0.61990000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -4153,7 +4149,7 @@
         <v>0.27079999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -4177,7 +4173,7 @@
         <v>0.57320000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -4201,7 +4197,7 @@
         <v>0.58879999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -4225,7 +4221,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -4249,7 +4245,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -4281,20 +4277,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AD93CD-4665-42DC-AC4B-4CF05C73D8EA}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.21875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="19"/>
+    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.1796875" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4326,7 +4322,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>158276</v>
       </c>
@@ -4359,7 +4355,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>158277</v>
       </c>
@@ -4392,7 +4388,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>158278</v>
       </c>
@@ -4425,7 +4421,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>158279</v>
       </c>
@@ -4458,7 +4454,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>158280</v>
       </c>
@@ -4491,7 +4487,7 @@
         <v>0.75139999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>158281</v>
       </c>
@@ -4524,7 +4520,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>158282</v>
       </c>
@@ -4557,7 +4553,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>158283</v>
       </c>
@@ -4590,7 +4586,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>158284</v>
       </c>
@@ -4623,7 +4619,7 @@
         <v>0.7762</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>158285</v>
       </c>
@@ -4656,7 +4652,7 @@
         <v>0.64429999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>158286</v>
       </c>
@@ -4689,7 +4685,7 @@
         <v>0.64429999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>158287</v>
       </c>
@@ -4722,7 +4718,7 @@
         <v>0.7762</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>111554</v>
       </c>
@@ -4755,7 +4751,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>111557</v>
       </c>
@@ -4788,7 +4784,7 @@
         <v>0.77129999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>111560</v>
       </c>
@@ -4821,7 +4817,7 @@
         <v>0.77969999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>111563</v>
       </c>
@@ -4854,7 +4850,7 @@
         <v>0.77710000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>111566</v>
       </c>
@@ -4887,7 +4883,7 @@
         <v>0.77529999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>111569</v>
       </c>
@@ -4920,7 +4916,7 @@
         <v>0.78269999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>111572</v>
       </c>
@@ -4953,7 +4949,7 @@
         <v>0.80820000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>111575</v>
       </c>
@@ -4986,7 +4982,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>111578</v>
       </c>
@@ -5019,7 +5015,7 @@
         <v>0.79990000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>111555</v>
       </c>
@@ -5052,7 +5048,7 @@
         <v>0.80110000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>111558</v>
       </c>
@@ -5085,7 +5081,7 @@
         <v>0.69830000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>111561</v>
       </c>
@@ -5118,7 +5114,7 @@
         <v>0.81010000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>111564</v>
       </c>
@@ -5151,7 +5147,7 @@
         <v>0.80789999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>111567</v>
       </c>
@@ -5184,7 +5180,7 @@
         <v>0.80640000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>111570</v>
       </c>
@@ -5217,7 +5213,7 @@
         <v>0.81269999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>111573</v>
       </c>
@@ -5250,7 +5246,7 @@
         <v>0.8347</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>111576</v>
       </c>
@@ -5283,7 +5279,7 @@
         <v>0.82940000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>111579</v>
       </c>
@@ -5316,7 +5312,7 @@
         <v>0.75219999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>131276</v>
       </c>
@@ -5349,7 +5345,7 @@
         <v>0.72450000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>131277</v>
       </c>
@@ -5382,7 +5378,7 @@
         <v>0.74180000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>131278</v>
       </c>
@@ -5415,7 +5411,7 @@
         <v>0.73729999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>131279</v>
       </c>
@@ -5448,7 +5444,7 @@
         <v>0.84570000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>131280</v>
       </c>
@@ -5481,7 +5477,7 @@
         <v>0.71609999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>131281</v>
       </c>
@@ -5514,7 +5510,7 @@
         <v>0.50470000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>119735</v>
       </c>
@@ -5547,7 +5543,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>116973</v>
       </c>
@@ -5580,7 +5576,7 @@
         <v>0.64200000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>116974</v>
       </c>
@@ -5613,7 +5609,7 @@
         <v>0.62580000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>116975</v>
       </c>
@@ -5646,7 +5642,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>121804</v>
       </c>
@@ -5679,7 +5675,7 @@
         <v>0.60219999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>121805</v>
       </c>
@@ -5712,7 +5708,7 @@
         <v>0.69630000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>121806</v>
       </c>
@@ -5745,7 +5741,7 @@
         <v>0.69630000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>121807</v>
       </c>
@@ -5788,20 +5784,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC118DC-A31E-40E5-8016-5940C6148308}">
   <dimension ref="A1:K79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="41.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="19"/>
+    <col min="1" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5836,7 +5832,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>271</v>
       </c>
@@ -5872,7 +5868,7 @@
         <v>0.78339999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>272</v>
       </c>
@@ -5908,7 +5904,7 @@
         <v>0.79090000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>273</v>
       </c>
@@ -5944,7 +5940,7 @@
         <v>0.7893</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -5980,7 +5976,7 @@
         <v>0.78959999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>275</v>
       </c>
@@ -6016,7 +6012,7 @@
         <v>0.78979999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>276</v>
       </c>
@@ -6052,7 +6048,7 @@
         <v>0.77080000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>277</v>
       </c>
@@ -6088,7 +6084,7 @@
         <v>0.78200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>278</v>
       </c>
@@ -6124,7 +6120,7 @@
         <v>0.78349999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>279</v>
       </c>
@@ -6160,7 +6156,7 @@
         <v>0.83450000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>280</v>
       </c>
@@ -6196,7 +6192,7 @@
         <v>0.81469999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>281</v>
       </c>
@@ -6232,7 +6228,7 @@
         <v>0.83289999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>282</v>
       </c>
@@ -6268,7 +6264,7 @@
         <v>0.83050000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>283</v>
       </c>
@@ -6304,7 +6300,7 @@
         <v>0.83069999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>299</v>
       </c>
@@ -6340,7 +6336,7 @@
         <v>0.81289999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>300</v>
       </c>
@@ -6376,7 +6372,7 @@
         <v>0.81940000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>301</v>
       </c>
@@ -6412,7 +6408,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>302</v>
       </c>
@@ -6448,7 +6444,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>303</v>
       </c>
@@ -6484,7 +6480,7 @@
         <v>0.81840000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>309</v>
       </c>
@@ -6520,7 +6516,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>310</v>
       </c>
@@ -6556,7 +6552,7 @@
         <v>0.82210000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>311</v>
       </c>
@@ -6592,7 +6588,7 @@
         <v>0.82330000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>315</v>
       </c>
@@ -6628,7 +6624,7 @@
         <v>0.82310000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>316</v>
       </c>
@@ -6664,7 +6660,7 @@
         <v>0.86150000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>319</v>
       </c>
@@ -6700,7 +6696,7 @@
         <v>0.85809999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>320</v>
       </c>
@@ -6736,7 +6732,7 @@
         <v>0.88700000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>321</v>
       </c>
@@ -6772,7 +6768,7 @@
         <v>0.88719999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>325</v>
       </c>
@@ -6808,7 +6804,7 @@
         <v>0.87719999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>327</v>
       </c>
@@ -6844,7 +6840,7 @@
         <v>0.86150000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>328</v>
       </c>
@@ -6880,7 +6876,7 @@
         <v>0.86629999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>331</v>
       </c>
@@ -6916,7 +6912,7 @@
         <v>0.86529999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -6952,7 +6948,7 @@
         <v>0.86539999999999995</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>334</v>
       </c>
@@ -6988,7 +6984,7 @@
         <v>0.86560000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>336</v>
       </c>
@@ -7024,7 +7020,7 @@
         <v>0.85340000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>337</v>
       </c>
@@ -7060,7 +7056,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>338</v>
       </c>
@@ -7096,7 +7092,7 @@
         <v>0.8649</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>341</v>
       </c>
@@ -7132,7 +7128,7 @@
         <v>0.86480000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>342</v>
       </c>
@@ -7168,7 +7164,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>345</v>
       </c>
@@ -7204,7 +7200,7 @@
         <v>0.87919999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>346</v>
       </c>
@@ -7240,7 +7236,7 @@
         <v>0.90159999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>347</v>
       </c>
@@ -7276,7 +7272,7 @@
         <v>0.90169999999999995</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>351</v>
       </c>
@@ -7312,7 +7308,7 @@
         <v>0.8931</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>355</v>
       </c>
@@ -7348,7 +7344,7 @@
         <v>0.8226</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>356</v>
       </c>
@@ -7384,7 +7380,7 @@
         <v>0.82569999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>357</v>
       </c>
@@ -7420,7 +7416,7 @@
         <v>0.82740000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>358</v>
       </c>
@@ -7456,7 +7452,7 @@
         <v>0.83079999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>359</v>
       </c>
@@ -7492,7 +7488,7 @@
         <v>0.83079999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>360</v>
       </c>
@@ -7528,7 +7524,7 @@
         <v>0.83460000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>361</v>
       </c>
@@ -7564,7 +7560,7 @@
         <v>0.82279999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>362</v>
       </c>
@@ -7600,7 +7596,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>363</v>
       </c>
@@ -7636,7 +7632,7 @@
         <v>0.82340000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>373</v>
       </c>
@@ -7672,7 +7668,7 @@
         <v>0.84460000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>374</v>
       </c>
@@ -7708,7 +7704,7 @@
         <v>0.84730000000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>375</v>
       </c>
@@ -7744,7 +7740,7 @@
         <v>0.8488</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>379</v>
       </c>
@@ -7780,7 +7776,7 @@
         <v>0.8518</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>380</v>
       </c>
@@ -7816,7 +7812,7 @@
         <v>0.8518</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>381</v>
       </c>
@@ -7852,7 +7848,7 @@
         <v>0.85519999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>385</v>
       </c>
@@ -7888,7 +7884,7 @@
         <v>0.8448</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>386</v>
       </c>
@@ -7924,7 +7920,7 @@
         <v>0.83950000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>389</v>
       </c>
@@ -7960,7 +7956,7 @@
         <v>0.84319999999999995</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>391</v>
       </c>
@@ -7996,7 +7992,7 @@
         <v>0.86380000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>393</v>
       </c>
@@ -8032,7 +8028,7 @@
         <v>0.86609999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>395</v>
       </c>
@@ -8068,7 +8064,7 @@
         <v>0.86739999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>397</v>
       </c>
@@ -8104,7 +8100,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>399</v>
       </c>
@@ -8140,7 +8136,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>401</v>
       </c>
@@ -8176,7 +8172,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>403</v>
       </c>
@@ -8212,7 +8208,7 @@
         <v>0.8639</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>405</v>
       </c>
@@ -8248,7 +8244,7 @@
         <v>0.8669</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>407</v>
       </c>
@@ -8284,7 +8280,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>409</v>
       </c>
@@ -8320,7 +8316,7 @@
         <v>0.80420000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>410</v>
       </c>
@@ -8356,7 +8352,7 @@
         <v>0.85129999999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>413</v>
       </c>
@@ -8392,7 +8388,7 @@
         <v>0.80420000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>415</v>
       </c>
@@ -8428,7 +8424,7 @@
         <v>0.86970000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>416</v>
       </c>
@@ -8464,7 +8460,7 @@
         <v>0.83460000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>419</v>
       </c>
@@ -8500,7 +8496,7 @@
         <v>0.81640000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>739</v>
       </c>
@@ -8536,7 +8532,7 @@
         <v>0.80530000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>741</v>
       </c>
@@ -8572,7 +8568,7 @@
         <v>0.80730000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>743</v>
       </c>
@@ -8608,7 +8604,7 @@
         <v>0.82440000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>745</v>
       </c>
@@ -8654,14 +8650,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75CEA00-E98C-48D1-8951-FCFD66D8871D}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" customWidth="1"/>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8681,7 +8677,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>605</v>
       </c>
@@ -8701,7 +8697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>607</v>
       </c>
@@ -8721,7 +8717,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>609</v>
       </c>
@@ -8741,7 +8737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>611</v>
       </c>
@@ -8761,7 +8757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>613</v>
       </c>
@@ -8781,7 +8777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>614</v>
       </c>
@@ -8801,7 +8797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>615</v>
       </c>
@@ -8821,7 +8817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>617</v>
       </c>
@@ -8841,7 +8837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>619</v>
       </c>
@@ -8861,7 +8857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>621</v>
       </c>
@@ -8881,7 +8877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>623</v>
       </c>
@@ -8901,7 +8897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>624</v>
       </c>
@@ -8921,7 +8917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>625</v>
       </c>
@@ -8941,7 +8937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>627</v>
       </c>
@@ -8961,7 +8957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>629</v>
       </c>
@@ -8981,7 +8977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>631</v>
       </c>
@@ -9009,21 +9005,21 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7291FE-1C80-46D5-A44B-ECDC4D68CA2E}">
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="19"/>
+    <col min="2" max="2" width="57.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" customWidth="1"/>
+    <col min="14" max="14" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9067,7 +9063,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -9112,7 +9108,7 @@
         <v>0.64549999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -9157,7 +9153,7 @@
         <v>0.53690000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -9202,7 +9198,7 @@
         <v>0.7571</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -9247,7 +9243,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -9292,7 +9288,7 @@
         <v>0.5766</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -9337,7 +9333,7 @@
         <v>0.61140000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -9382,7 +9378,7 @@
         <v>0.73450000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -9427,7 +9423,7 @@
         <v>0.51990000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -9472,7 +9468,7 @@
         <v>0.59840000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -9517,7 +9513,7 @@
         <v>0.63500000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -9562,7 +9558,7 @@
         <v>0.71589999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -9607,7 +9603,7 @@
         <v>0.54020000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -9652,7 +9648,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -9697,7 +9693,7 @@
         <v>0.50380000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -9742,7 +9738,7 @@
         <v>0.72240000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -9787,7 +9783,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -9832,7 +9828,7 @@
         <v>0.53280000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>121</v>
       </c>
@@ -9877,7 +9873,7 @@
         <v>0.60260000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>123</v>
       </c>
@@ -9922,7 +9918,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -9967,7 +9963,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -10012,7 +10008,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -10057,7 +10053,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -10102,7 +10098,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -10147,7 +10143,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -10192,7 +10188,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -10237,7 +10233,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>141</v>
       </c>
@@ -10282,7 +10278,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -10327,7 +10323,7 @@
         <v>0.58209999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -10372,7 +10368,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -10417,7 +10413,7 @@
         <v>0.50380000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -10462,7 +10458,7 @@
         <v>0.72240000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -10507,7 +10503,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -10552,7 +10548,7 @@
         <v>0.53280000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -10597,7 +10593,7 @@
         <v>0.60260000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -10642,7 +10638,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -10687,7 +10683,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -10732,7 +10728,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -10777,7 +10773,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -10822,7 +10818,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -10867,7 +10863,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -10912,7 +10908,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>137</v>
       </c>
@@ -10957,7 +10953,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -11002,7 +10998,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>143</v>
       </c>
@@ -11047,7 +11043,7 @@
         <v>0.58209999999999995</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -11092,7 +11088,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -11137,7 +11133,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -11182,7 +11178,7 @@
         <v>0.73450000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -11227,7 +11223,7 @@
         <v>0.54020000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>129</v>
       </c>
@@ -11272,7 +11268,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -11317,7 +11313,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -11362,7 +11358,7 @@
         <v>0.54630000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -11407,7 +11403,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>145</v>
       </c>
@@ -11462,16 +11458,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E191415-7327-4CFF-B229-D7F54ABBDB32}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" customWidth="1"/>
+    <col min="6" max="6" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11491,7 +11487,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>169</v>
       </c>
@@ -11520,15 +11516,15 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25522428-B4D4-43A2-8ABC-2052B8318014}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="30.5546875" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="30.54296875" customWidth="1"/>
+    <col min="6" max="6" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11548,7 +11544,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>167</v>
       </c>
@@ -11577,17 +11573,17 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A5EDD5-EC5E-4B4D-BAE8-EF24A4D32E1E}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.77734375" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11607,7 +11603,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -11637,15 +11633,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="57.5546875" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="57.54296875" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11668,7 +11664,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>425</v>
       </c>
@@ -11691,7 +11687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>427</v>
       </c>
@@ -11714,7 +11710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>429</v>
       </c>
@@ -11737,7 +11733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>430</v>
       </c>
@@ -11760,7 +11756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>431</v>
       </c>
@@ -11783,7 +11779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>432</v>
       </c>
@@ -11806,7 +11802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>433</v>
       </c>
@@ -11829,7 +11825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>434</v>
       </c>
@@ -11852,7 +11848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>435</v>
       </c>
@@ -11875,7 +11871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>436</v>
       </c>
@@ -11898,7 +11894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>445</v>
       </c>
@@ -11921,7 +11917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>446</v>
       </c>
@@ -11944,7 +11940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -11967,7 +11963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>448</v>
       </c>
@@ -11990,7 +11986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>449</v>
       </c>
@@ -12013,7 +12009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>450</v>
       </c>
@@ -12036,7 +12032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>457</v>
       </c>
@@ -12059,7 +12055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>459</v>
       </c>
@@ -12082,7 +12078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>461</v>
       </c>
@@ -12105,7 +12101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>463</v>
       </c>
@@ -12128,7 +12124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>464</v>
       </c>
@@ -12151,7 +12147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>467</v>
       </c>
@@ -12174,7 +12170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>468</v>
       </c>
@@ -12197,7 +12193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>469</v>
       </c>
@@ -12220,7 +12216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>473</v>
       </c>
@@ -12243,7 +12239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>475</v>
       </c>
@@ -12266,7 +12262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>477</v>
       </c>
@@ -12289,7 +12285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>479</v>
       </c>
@@ -12312,7 +12308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>480</v>
       </c>
@@ -12335,7 +12331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>483</v>
       </c>
@@ -12358,7 +12354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>485</v>
       </c>
@@ -12381,7 +12377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>487</v>
       </c>
@@ -12404,7 +12400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>488</v>
       </c>
@@ -12427,7 +12423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>491</v>
       </c>
@@ -12450,7 +12446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>493</v>
       </c>
@@ -12473,7 +12469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>494</v>
       </c>
@@ -12496,7 +12492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>495</v>
       </c>
@@ -12519,7 +12515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>496</v>
       </c>
@@ -12542,7 +12538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>497</v>
       </c>
@@ -12565,7 +12561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>498</v>
       </c>
@@ -12588,7 +12584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>499</v>
       </c>
@@ -12611,7 +12607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>507</v>
       </c>
@@ -12634,7 +12630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>509</v>
       </c>
@@ -12657,7 +12653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>511</v>
       </c>
@@ -12680,7 +12676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>513</v>
       </c>
@@ -12703,7 +12699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>515</v>
       </c>
@@ -12726,7 +12722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>516</v>
       </c>
@@ -12749,7 +12745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>517</v>
       </c>
@@ -12772,7 +12768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>518</v>
       </c>
@@ -12795,7 +12791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>519</v>
       </c>
@@ -12818,7 +12814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>525</v>
       </c>
@@ -12841,7 +12837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>526</v>
       </c>
@@ -12864,7 +12860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>529</v>
       </c>
@@ -12887,7 +12883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>531</v>
       </c>
@@ -12910,7 +12906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>532</v>
       </c>
@@ -12933,7 +12929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>533</v>
       </c>
@@ -12956,7 +12952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>535</v>
       </c>
@@ -12979,7 +12975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>537</v>
       </c>
@@ -13002,7 +12998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>539</v>
       </c>
@@ -13025,7 +13021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>541</v>
       </c>
@@ -13048,7 +13044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>543</v>
       </c>
@@ -13071,7 +13067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>544</v>
       </c>
@@ -13094,7 +13090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>545</v>
       </c>
@@ -13117,7 +13113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>546</v>
       </c>
@@ -13140,7 +13136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>551</v>
       </c>
@@ -13163,7 +13159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>553</v>
       </c>
@@ -13186,7 +13182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>555</v>
       </c>
@@ -13209,7 +13205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>557</v>
       </c>
@@ -13232,7 +13228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>558</v>
       </c>
@@ -13255,7 +13251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>559</v>
       </c>
@@ -13278,7 +13274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>560</v>
       </c>
@@ -13301,7 +13297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>563</v>
       </c>
@@ -13324,7 +13320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>564</v>
       </c>
@@ -13347,7 +13343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>565</v>
       </c>
@@ -13370,7 +13366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>566</v>
       </c>
@@ -13393,7 +13389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>567</v>
       </c>
@@ -13416,7 +13412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>573</v>
       </c>
@@ -13439,7 +13435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>575</v>
       </c>
@@ -13462,7 +13458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>576</v>
       </c>
@@ -13485,7 +13481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>577</v>
       </c>
@@ -13508,7 +13504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -13531,7 +13527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>583</v>
       </c>
@@ -13554,7 +13550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>585</v>
       </c>
@@ -13577,7 +13573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>587</v>
       </c>
@@ -13600,7 +13596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>589</v>
       </c>
@@ -13623,7 +13619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>591</v>
       </c>
@@ -13646,7 +13642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>593</v>
       </c>
@@ -13669,7 +13665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>595</v>
       </c>
@@ -13692,7 +13688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>597</v>
       </c>
@@ -13715,7 +13711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>599</v>
       </c>
@@ -13738,7 +13734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>600</v>
       </c>
@@ -13761,7 +13757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>601</v>
       </c>
@@ -13800,19 +13796,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0952EC0-78E2-4227-94D1-113308784769}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -13841,7 +13837,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -13871,7 +13867,7 @@
         <v>0.50009999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -13901,7 +13897,7 @@
         <v>0.5181</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -13931,7 +13927,7 @@
         <v>0.51949999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -13961,7 +13957,7 @@
         <v>0.59840000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -13991,7 +13987,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -14021,7 +14017,7 @@
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -14059,17 +14055,17 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE280E8-1030-4D15-BB87-39545B71D8FE}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14092,7 +14088,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -14116,7 +14112,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -14148,15 +14144,15 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC3D159-7610-47A2-B6E6-4BC8DBFBC056}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
     <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14176,7 +14172,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>633</v>
       </c>
@@ -14196,7 +14192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>635</v>
       </c>
@@ -14216,7 +14212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>637</v>
       </c>
@@ -14236,7 +14232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>639</v>
       </c>
@@ -14256,7 +14252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>641</v>
       </c>
@@ -14276,7 +14272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>643</v>
       </c>
@@ -14296,7 +14292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>645</v>
       </c>
@@ -14316,7 +14312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>647</v>
       </c>
@@ -14336,7 +14332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>649</v>
       </c>
@@ -14356,7 +14352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>651</v>
       </c>
@@ -14376,7 +14372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>653</v>
       </c>
@@ -14396,7 +14392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>655</v>
       </c>
@@ -14416,7 +14412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>657</v>
       </c>
@@ -14436,7 +14432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>659</v>
       </c>
@@ -14456,7 +14452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>660</v>
       </c>
@@ -14484,14 +14480,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA1586A9-3200-4887-94DE-CCF39E21CB1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="22" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14502,7 +14498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>750</v>
       </c>
@@ -14513,7 +14509,7 @@
         <v>8841</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>752</v>
       </c>
@@ -14524,7 +14520,7 @@
         <v>12406</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>754</v>
       </c>
@@ -14535,7 +14531,7 @@
         <v>9150</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>755</v>
       </c>
@@ -14554,15 +14550,15 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D45C86-8F36-4726-BB8C-72524168E246}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14582,7 +14578,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>662</v>
       </c>
@@ -14602,7 +14598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>664</v>
       </c>
@@ -14622,7 +14618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>666</v>
       </c>
@@ -14642,7 +14638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>668</v>
       </c>
@@ -14662,7 +14658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>670</v>
       </c>
@@ -14682,7 +14678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>672</v>
       </c>
@@ -14702,7 +14698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>674</v>
       </c>
@@ -14722,7 +14718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>675</v>
       </c>
@@ -14742,7 +14738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>677</v>
       </c>
@@ -14771,16 +14767,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C460FD-853F-48A8-BB18-DB58CBD5BD31}">
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14797,7 +14793,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -14815,7 +14811,7 @@
         <v>0.53449999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -14833,7 +14829,7 @@
         <v>0.50009999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -14851,7 +14847,7 @@
         <v>0.5181</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -14869,7 +14865,7 @@
         <v>0.56310000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -14887,7 +14883,7 @@
         <v>0.69259999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -14905,7 +14901,7 @@
         <v>0.58479999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -14923,7 +14919,7 @@
         <v>0.52429999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -14941,7 +14937,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -14959,7 +14955,7 @@
         <v>0.51949999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -14977,7 +14973,7 @@
         <v>0.59850000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -14995,7 +14991,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -15013,7 +15009,7 @@
         <v>0.61990000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -15031,7 +15027,7 @@
         <v>0.64549999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -15049,7 +15045,7 @@
         <v>0.53690000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -15067,7 +15063,7 @@
         <v>0.75700000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -15085,7 +15081,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -15103,7 +15099,7 @@
         <v>0.5766</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -15121,7 +15117,7 @@
         <v>0.61140000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -15139,7 +15135,7 @@
         <v>0.73440000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -15157,7 +15153,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -15175,7 +15171,7 @@
         <v>0.59860000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -15193,7 +15189,7 @@
         <v>0.6351</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -15211,7 +15207,7 @@
         <v>0.71599999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -15229,7 +15225,7 @@
         <v>0.5403</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -15247,7 +15243,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -15265,7 +15261,7 @@
         <v>0.79559999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -15283,7 +15279,7 @@
         <v>0.73480000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -15301,7 +15297,7 @@
         <v>0.71530000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -15319,7 +15315,7 @@
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -15337,7 +15333,7 @@
         <v>0.64339999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -15355,7 +15351,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -15373,7 +15369,7 @@
         <v>0.62250000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -15391,7 +15387,7 @@
         <v>0.54469999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -15409,7 +15405,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -15427,7 +15423,7 @@
         <v>0.58220000000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -15445,7 +15441,7 @@
         <v>0.51819999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -15463,7 +15459,7 @@
         <v>0.27089999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -15481,7 +15477,7 @@
         <v>0.57320000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -15499,7 +15495,7 @@
         <v>0.58879999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -15517,7 +15513,7 @@
         <v>0.48780000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -15535,7 +15531,7 @@
         <v>0.5796</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -15553,7 +15549,7 @@
         <v>0.57920000000000005</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -15571,7 +15567,7 @@
         <v>0.60460000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -15589,7 +15585,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -15607,7 +15603,7 @@
         <v>0.65529999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -15625,7 +15621,7 @@
         <v>0.53590000000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -15643,7 +15639,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -15661,7 +15657,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -15679,7 +15675,7 @@
         <v>0.58109999999999995</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>81</v>
       </c>
@@ -15697,7 +15693,7 @@
         <v>0.48780000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -15715,7 +15711,7 @@
         <v>0.5796</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>101</v>
       </c>
@@ -15733,7 +15729,7 @@
         <v>0.60860000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -15751,7 +15747,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -15769,7 +15765,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -15787,7 +15783,7 @@
         <v>0.59009999999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -15805,7 +15801,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>109</v>
       </c>
@@ -15823,7 +15819,7 @@
         <v>0.70830000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -15841,7 +15837,7 @@
         <v>0.64939999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -15859,7 +15855,7 @@
         <v>0.50370000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -15877,7 +15873,7 @@
         <v>0.72250000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -15895,7 +15891,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -15913,7 +15909,7 @@
         <v>0.53269999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -15931,7 +15927,7 @@
         <v>0.60270000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>123</v>
       </c>
@@ -15949,7 +15945,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>125</v>
       </c>
@@ -15967,7 +15963,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -15985,7 +15981,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -16003,7 +15999,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>131</v>
       </c>
@@ -16021,7 +16017,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>133</v>
       </c>
@@ -16039,7 +16035,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>135</v>
       </c>
@@ -16057,7 +16053,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>137</v>
       </c>
@@ -16075,7 +16071,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>139</v>
       </c>
@@ -16093,7 +16089,7 @@
         <v>0.67789999999999995</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>141</v>
       </c>
@@ -16111,7 +16107,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>143</v>
       </c>
@@ -16129,7 +16125,7 @@
         <v>0.58220000000000005</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>145</v>
       </c>
@@ -16147,7 +16143,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>147</v>
       </c>
@@ -16165,7 +16161,7 @@
         <v>0.53210000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>149</v>
       </c>
@@ -16183,7 +16179,7 @@
         <v>0.4556</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>151</v>
       </c>
@@ -16201,7 +16197,7 @@
         <v>0.52790000000000004</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>153</v>
       </c>
@@ -16219,7 +16215,7 @@
         <v>0.53380000000000005</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -16237,7 +16233,7 @@
         <v>0.59209999999999996</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>157</v>
       </c>
@@ -16255,7 +16251,7 @@
         <v>0.48980000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -16273,7 +16269,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>161</v>
       </c>
@@ -16291,7 +16287,7 @@
         <v>0.49159999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -16309,7 +16305,7 @@
         <v>0.49249999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -16327,7 +16323,7 @@
         <v>0.64149999999999996</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -16345,7 +16341,7 @@
         <v>0.87329999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>169</v>
       </c>
@@ -16363,7 +16359,7 @@
         <v>0.64270000000000005</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>171</v>
       </c>
@@ -16381,7 +16377,7 @@
         <v>0.68020000000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>173</v>
       </c>
@@ -16399,7 +16395,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>175</v>
       </c>
@@ -16417,7 +16413,7 @@
         <v>0.64359999999999995</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>177</v>
       </c>
@@ -16435,7 +16431,7 @@
         <v>0.66600000000000004</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>179</v>
       </c>
@@ -16453,7 +16449,7 @@
         <v>0.65149999999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>181</v>
       </c>
@@ -16481,15 +16477,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EC6327-8CBD-476A-BB08-5C75376F1333}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -16506,7 +16502,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -16524,7 +16520,7 @@
         <v>0.49159999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -16550,15 +16546,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF069F-11F0-41FB-B939-51B5F45B8CB2}">
   <dimension ref="A1:E111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -16575,7 +16571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>689</v>
       </c>
@@ -16592,7 +16588,7 @@
         <v>103121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>690</v>
       </c>
@@ -16609,7 +16605,7 @@
         <v>118541</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>691</v>
       </c>
@@ -16626,7 +16622,7 @@
         <v>135356</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>692</v>
       </c>
@@ -16643,7 +16639,7 @@
         <v>128574</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>693</v>
       </c>
@@ -16660,7 +16656,7 @@
         <v>145962</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>694</v>
       </c>
@@ -16677,7 +16673,7 @@
         <v>163173</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>696</v>
       </c>
@@ -16694,7 +16690,7 @@
         <v>115840</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>697</v>
       </c>
@@ -16711,7 +16707,7 @@
         <v>131702</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>698</v>
       </c>
@@ -16728,7 +16724,7 @@
         <v>148391</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>699</v>
       </c>
@@ -16745,7 +16741,7 @@
         <v>141557</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>700</v>
       </c>
@@ -16762,7 +16758,7 @@
         <v>159273</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>701</v>
       </c>
@@ -16779,7 +16775,7 @@
         <v>178319</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>702</v>
       </c>
@@ -16796,583 +16792,583 @@
         <v>7067</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="11"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="11"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="11"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="11"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="11"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="11"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="11"/>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="11"/>
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="11"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="11"/>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="11"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="11"/>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="11"/>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="11"/>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="11"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="11"/>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="11"/>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="11"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="11"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="11"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="11"/>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="11"/>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="11"/>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="11"/>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="11"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="11"/>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="11"/>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="11"/>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="11"/>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="11"/>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="11"/>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="11"/>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="11"/>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="11"/>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="11"/>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
@@ -17386,17 +17382,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E21284-68D2-4B7C-8891-F33FB2D4174C}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
     <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="19"/>
+    <col min="8" max="8" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17422,7 +17418,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -17449,7 +17445,7 @@
         <v>0.54469999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -17476,7 +17472,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -17503,7 +17499,7 @@
         <v>0.58230000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -17530,7 +17526,7 @@
         <v>0.51819999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -17557,7 +17553,7 @@
         <v>0.4879</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -17592,16 +17588,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7C1833-5DC7-4038-9B0D-2D47C7DFB4A9}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="19"/>
+    <col min="6" max="6" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17621,7 +17617,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -17642,7 +17638,7 @@
         <v>0.56310000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -17671,18 +17667,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6578FDA-80BC-4521-8BA7-3C8BD0257781}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="19"/>
+    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17708,7 +17704,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -17735,7 +17731,7 @@
         <v>0.60460000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -17762,7 +17758,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -17789,7 +17785,7 @@
         <v>0.65529999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -17816,7 +17812,7 @@
         <v>0.53590000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -17843,7 +17839,7 @@
         <v>0.4879</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -17878,17 +17874,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC341ECE-6FE5-41E4-9F6E-2DB5B33BB710}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17911,7 +17907,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -17935,7 +17931,7 @@
         <v>0.60860000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -17959,7 +17955,7 @@
         <v>0.5827</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -17983,7 +17979,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>107</v>
       </c>

--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eaton-my.sharepoint.com/personal/arelycastillo_eaton_com/Documents/Documents/GitHub/Eaton/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33750515-3870-4167-971B-F7306F2CBFE4}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C53D82F-0031-4DDF-AF9D-39F9D4B0D0C0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="18" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura" sheetId="9" r:id="rId1"/>
@@ -11631,7 +11631,6 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11664,7 +11663,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>425</v>
       </c>
@@ -11687,7 +11686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>427</v>
       </c>
@@ -11710,7 +11709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>429</v>
       </c>
@@ -11733,7 +11732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>430</v>
       </c>
@@ -11756,7 +11755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>431</v>
       </c>
@@ -11779,7 +11778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>432</v>
       </c>
@@ -11802,7 +11801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>433</v>
       </c>
@@ -11825,7 +11824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>434</v>
       </c>
@@ -11848,7 +11847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>435</v>
       </c>
@@ -11871,7 +11870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>436</v>
       </c>
@@ -11894,7 +11893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>445</v>
       </c>
@@ -11917,7 +11916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>446</v>
       </c>
@@ -11940,7 +11939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -11963,7 +11962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>448</v>
       </c>
@@ -11986,7 +11985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>449</v>
       </c>
@@ -12354,7 +12353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>485</v>
       </c>
@@ -12377,7 +12376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>487</v>
       </c>
@@ -12400,7 +12399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>488</v>
       </c>
@@ -12423,7 +12422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>491</v>
       </c>
@@ -12446,7 +12445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>493</v>
       </c>
@@ -12469,7 +12468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>494</v>
       </c>
@@ -12492,7 +12491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>495</v>
       </c>
@@ -12515,7 +12514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>496</v>
       </c>
@@ -12538,7 +12537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>497</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>498</v>
       </c>
@@ -12584,7 +12583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>499</v>
       </c>
@@ -12607,7 +12606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>507</v>
       </c>
@@ -12630,7 +12629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>509</v>
       </c>
@@ -12653,7 +12652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>511</v>
       </c>
@@ -12676,7 +12675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>513</v>
       </c>
@@ -12699,7 +12698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>515</v>
       </c>
@@ -12722,7 +12721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>516</v>
       </c>
@@ -12745,7 +12744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>517</v>
       </c>
@@ -12768,7 +12767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>518</v>
       </c>
@@ -12791,7 +12790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>519</v>
       </c>
@@ -12814,7 +12813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>525</v>
       </c>
@@ -12837,7 +12836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>526</v>
       </c>
@@ -12860,7 +12859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>529</v>
       </c>
@@ -12883,7 +12882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>531</v>
       </c>
@@ -12906,7 +12905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>532</v>
       </c>
@@ -12929,7 +12928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>533</v>
       </c>
@@ -13297,7 +13296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>563</v>
       </c>
@@ -13320,7 +13319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>564</v>
       </c>
@@ -13343,7 +13342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>565</v>
       </c>
@@ -13366,7 +13365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>566</v>
       </c>
@@ -13389,7 +13388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>567</v>
       </c>
@@ -13412,7 +13411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>573</v>
       </c>
@@ -13435,7 +13434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>575</v>
       </c>
@@ -13458,7 +13457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>576</v>
       </c>
@@ -13481,7 +13480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>577</v>
       </c>
@@ -13781,13 +13780,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G93" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G93" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eaton-my.sharepoint.com/personal/arelycastillo_eaton_com/Documents/Documents/GitHub/Eaton/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C53D82F-0031-4DDF-AF9D-39F9D4B0D0C0}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE11FF66-5101-4E97-ABF3-21CB180E892A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="18" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura" sheetId="9" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="765">
   <si>
     <t>Catalogo</t>
   </si>
@@ -2461,7 +2461,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2502,6 +2502,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2520,6 +2526,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16538,16 +16548,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF069F-11F0-41FB-B939-51B5F45B8CB2}">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="17" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -16560,11 +16572,17 @@
       <c r="D1" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="26" t="s">
+        <v>747</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G1" s="24" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>689</v>
       </c>
@@ -16577,11 +16595,19 @@
       <c r="D2" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="27">
+        <f>1605.72*18</f>
+        <v>28902.959999999999</v>
+      </c>
+      <c r="F2" s="12">
         <v>103121</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G2" s="19">
+        <f>ROUND(((F2-E2)/F2),4)</f>
+        <v>0.71970000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>690</v>
       </c>
@@ -16594,11 +16620,19 @@
       <c r="D3" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="27">
+        <f>2372.73*18</f>
+        <v>42709.14</v>
+      </c>
+      <c r="F3" s="12">
         <v>118541</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="19">
+        <f t="shared" ref="G3:G14" si="0">ROUND(((F3-E3)/F3),4)</f>
+        <v>0.63970000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>691</v>
       </c>
@@ -16611,11 +16645,19 @@
       <c r="D4" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="27">
+        <f>2482.17*18</f>
+        <v>44679.06</v>
+      </c>
+      <c r="F4" s="12">
         <v>135356</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G4" s="19">
+        <f t="shared" si="0"/>
+        <v>0.66990000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>692</v>
       </c>
@@ -16628,11 +16670,19 @@
       <c r="D5" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="27">
+        <f>2081.55*18</f>
+        <v>37467.9</v>
+      </c>
+      <c r="F5" s="12">
         <v>128574</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5" s="19">
+        <f t="shared" si="0"/>
+        <v>0.70860000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>693</v>
       </c>
@@ -16645,11 +16695,19 @@
       <c r="D6" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="27">
+        <f>3365*18</f>
+        <v>60570</v>
+      </c>
+      <c r="F6" s="12">
         <v>145962</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G6" s="19">
+        <f t="shared" si="0"/>
+        <v>0.58499999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>694</v>
       </c>
@@ -16662,11 +16720,19 @@
       <c r="D7" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="27">
+        <f>3762.16*18</f>
+        <v>67718.880000000005</v>
+      </c>
+      <c r="F7" s="12">
         <v>163173</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="19">
+        <f t="shared" si="0"/>
+        <v>0.58499999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>696</v>
       </c>
@@ -16679,11 +16745,19 @@
       <c r="D8" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="27">
+        <f>1749.21*18</f>
+        <v>31485.78</v>
+      </c>
+      <c r="F8" s="12">
         <v>115840</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G8" s="19">
+        <f t="shared" si="0"/>
+        <v>0.72819999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>697</v>
       </c>
@@ -16696,11 +16770,19 @@
       <c r="D9" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="27">
+        <f>2535.37*18</f>
+        <v>45636.659999999996</v>
+      </c>
+      <c r="F9" s="12">
         <v>131702</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.65349999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>698</v>
       </c>
@@ -16713,11 +16795,19 @@
       <c r="D10" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="27">
+        <f>2644.81*18</f>
+        <v>47606.58</v>
+      </c>
+      <c r="F10" s="12">
         <v>148391</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G10" s="19">
+        <f t="shared" si="0"/>
+        <v>0.67920000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>699</v>
       </c>
@@ -16730,11 +16820,19 @@
       <c r="D11" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="27">
+        <f>2225.04*18</f>
+        <v>40050.720000000001</v>
+      </c>
+      <c r="F11" s="12">
         <v>141557</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G11" s="19">
+        <f t="shared" si="0"/>
+        <v>0.71709999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>700</v>
       </c>
@@ -16747,11 +16845,19 @@
       <c r="D12" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="27">
+        <f>3527.64*18</f>
+        <v>63497.52</v>
+      </c>
+      <c r="F12" s="12">
         <v>159273</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G12" s="19">
+        <f t="shared" si="0"/>
+        <v>0.60129999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>701</v>
       </c>
@@ -16764,11 +16870,19 @@
       <c r="D13" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="27">
+        <f>3924.8*18</f>
+        <v>70646.400000000009</v>
+      </c>
+      <c r="F13" s="12">
         <v>178319</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G13" s="19">
+        <f t="shared" si="0"/>
+        <v>0.6038</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>702</v>
       </c>
@@ -16781,591 +16895,696 @@
       <c r="D14" t="s">
         <v>703</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="17">
+        <f>309.63*18</f>
+        <v>5573.34</v>
+      </c>
+      <c r="F14" s="12">
         <v>7067</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G14" s="19">
+        <f t="shared" si="0"/>
+        <v>0.2114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E15" s="27"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16" s="27"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E17" s="27"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E18" s="27"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19" s="27"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20" s="27"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E21" s="27"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22" s="27"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E24" s="27"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E25" s="27"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E26" s="27"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E27" s="27"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E29" s="27"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E30" s="27"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E31" s="27"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E32" s="27"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E33" s="27"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E34" s="27"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E35" s="27"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E36" s="27"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E37" s="27"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E38" s="27"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E39" s="27"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E40" s="27"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E41" s="27"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E42" s="27"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E43" s="27"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E44" s="27"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E45" s="27"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E46" s="27"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E47" s="27"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E48" s="27"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E49" s="27"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E50" s="27"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E51" s="27"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E52" s="27"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E53" s="27"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E54" s="27"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E55" s="27"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E56" s="27"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E57" s="27"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E58" s="27"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E59" s="27"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E60" s="27"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E61" s="27"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E62" s="27"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E63" s="27"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E64" s="27"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E65" s="27"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E66" s="27"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="11"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E67" s="27"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="11"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E68" s="27"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="11"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E69" s="27"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E70" s="27"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E71" s="27"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="11"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E72" s="27"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="11"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E73" s="27"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="11"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E74" s="27"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E75" s="27"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="11"/>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E76" s="27"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E77" s="27"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E78" s="27"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="11"/>
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E79" s="27"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E80" s="27"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="11"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E81" s="27"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="11"/>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E82" s="27"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="11"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E83" s="27"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E84" s="27"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="11"/>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E85" s="27"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="11"/>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E86" s="27"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="11"/>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E87" s="27"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="11"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E88" s="27"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="11"/>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E89" s="27"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="11"/>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E90" s="27"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="11"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E91" s="27"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="11"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E92" s="27"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="11"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E93" s="27"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="11"/>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E94" s="27"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="11"/>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E95" s="27"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="11"/>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E96" s="27"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E97" s="27"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="11"/>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E98" s="27"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="11"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E99" s="27"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="11"/>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E100" s="27"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="11"/>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E101" s="27"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E102" s="27"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="11"/>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E103" s="27"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="11"/>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E104" s="27"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="11"/>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E105" s="27"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="11"/>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E106" s="27"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E107" s="27"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="11"/>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E108" s="27"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="11"/>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E109" s="27"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="11"/>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E110" s="27"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="11"/>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
+      <c r="E111" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eaton-my.sharepoint.com/personal/arelycastillo_eaton_com/Documents/Documents/GitHub/Eaton/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE11FF66-5101-4E97-ABF3-21CB180E892A}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="8_{FA424185-D530-44FF-BEF1-1D3F8B302D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC2FCA90-0A45-4B3D-A4E6-0B0A80A76808}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="20" xr2:uid="{E356A83D-CAB3-4D69-8690-2DF2AB7B7938}"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,8 @@
     <sheet name="SV" sheetId="19" r:id="rId20"/>
     <sheet name="K" sheetId="7" r:id="rId21"/>
     <sheet name="Medidores" sheetId="27" r:id="rId22"/>
-    <sheet name="L" sheetId="8" r:id="rId23"/>
+    <sheet name="Sheet1" sheetId="28" r:id="rId23"/>
+    <sheet name="L" sheetId="8" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">BZM!$A$1:$I$45</definedName>
@@ -44,7 +45,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Lista!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">PDG!$A$1:$I$79</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294872311" uniqueCount="765">
   <si>
     <t>Catalogo</t>
   </si>
@@ -2850,15 +2851,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7A467A-8250-4705-9EA7-960D198EF57F}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2884,7 +2885,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>0.53449999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -2932,7 +2933,7 @@
         <v>0.62250000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -2956,7 +2957,7 @@
         <v>0.57920000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -2983,7 +2984,7 @@
         <v>0.68020000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>173</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>175</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>0.64359999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>0.66600000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>179</v>
       </c>
@@ -3091,7 +3092,7 @@
         <v>0.65149999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>181</v>
       </c>
@@ -3126,15 +3127,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB46B0E-37A5-4181-9C58-3C1127A0CA35}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="19"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3157,7 +3158,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -3181,7 +3182,7 @@
         <v>0.79630000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>0.71460000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>0.60109999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -3277,7 +3278,7 @@
         <v>0.64329999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -3301,7 +3302,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -3373,7 +3374,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>155</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -3421,7 +3422,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>159</v>
       </c>
@@ -3445,7 +3446,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -3469,7 +3470,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -3493,7 +3494,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -3541,7 +3542,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -3589,7 +3590,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -3613,7 +3614,7 @@
         <v>0.79630000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -3637,7 +3638,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -3661,7 +3662,7 @@
         <v>0.71460000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>0.60109999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -3709,7 +3710,7 @@
         <v>0.64329999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>149</v>
       </c>
@@ -3757,7 +3758,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>151</v>
       </c>
@@ -3781,7 +3782,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -3805,7 +3806,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>155</v>
       </c>
@@ -3829,7 +3830,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>157</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>159</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v>0.7016</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>149</v>
       </c>
@@ -3901,7 +3902,7 @@
         <v>0.45379999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>151</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>0.52829999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -3949,7 +3950,7 @@
         <v>0.53500000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>0.59130000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -3997,7 +3998,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>159</v>
       </c>
@@ -4030,17 +4031,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D487D21-F885-403B-A303-1EC36DC187C1}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="19"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4087,7 +4088,7 @@
         <v>0.58479999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -4111,7 +4112,7 @@
         <v>0.52429999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>0.61990000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>0.27079999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>0.57320000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -4207,7 +4208,7 @@
         <v>0.58879999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -4255,7 +4256,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -4287,20 +4288,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AD93CD-4665-42DC-AC4B-4CF05C73D8EA}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.1796875" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" style="19"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4332,7 +4333,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>158276</v>
       </c>
@@ -4365,7 +4366,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>158277</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>158278</v>
       </c>
@@ -4431,7 +4432,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>158279</v>
       </c>
@@ -4464,7 +4465,7 @@
         <v>0.73360000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>158280</v>
       </c>
@@ -4497,7 +4498,7 @@
         <v>0.75139999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>158281</v>
       </c>
@@ -4530,7 +4531,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>158282</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>158283</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>0.75129999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>158284</v>
       </c>
@@ -4629,7 +4630,7 @@
         <v>0.7762</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>158285</v>
       </c>
@@ -4662,7 +4663,7 @@
         <v>0.64429999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>158286</v>
       </c>
@@ -4695,7 +4696,7 @@
         <v>0.64429999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>158287</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v>0.7762</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>111554</v>
       </c>
@@ -4761,7 +4762,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>111557</v>
       </c>
@@ -4794,7 +4795,7 @@
         <v>0.77129999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>111560</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>0.77969999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>111563</v>
       </c>
@@ -4860,7 +4861,7 @@
         <v>0.77710000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>111566</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>0.77529999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>111569</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>0.78269999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>111572</v>
       </c>
@@ -4959,7 +4960,7 @@
         <v>0.80820000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>111575</v>
       </c>
@@ -4992,7 +4993,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>111578</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>0.79990000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>111555</v>
       </c>
@@ -5058,7 +5059,7 @@
         <v>0.80110000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>111558</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>0.69830000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>111561</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v>0.81010000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>111564</v>
       </c>
@@ -5157,7 +5158,7 @@
         <v>0.80789999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>111567</v>
       </c>
@@ -5190,7 +5191,7 @@
         <v>0.80640000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>111570</v>
       </c>
@@ -5223,7 +5224,7 @@
         <v>0.81269999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>111573</v>
       </c>
@@ -5256,7 +5257,7 @@
         <v>0.8347</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>111576</v>
       </c>
@@ -5289,7 +5290,7 @@
         <v>0.82940000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>111579</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>0.75219999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>131276</v>
       </c>
@@ -5355,7 +5356,7 @@
         <v>0.72450000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>131277</v>
       </c>
@@ -5388,7 +5389,7 @@
         <v>0.74180000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>131278</v>
       </c>
@@ -5421,7 +5422,7 @@
         <v>0.73729999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>131279</v>
       </c>
@@ -5454,7 +5455,7 @@
         <v>0.84570000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>131280</v>
       </c>
@@ -5487,7 +5488,7 @@
         <v>0.71609999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>131281</v>
       </c>
@@ -5520,7 +5521,7 @@
         <v>0.50470000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>119735</v>
       </c>
@@ -5553,7 +5554,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>116973</v>
       </c>
@@ -5586,7 +5587,7 @@
         <v>0.64200000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>116974</v>
       </c>
@@ -5619,7 +5620,7 @@
         <v>0.62580000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>116975</v>
       </c>
@@ -5652,7 +5653,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>121804</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>0.60219999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>121805</v>
       </c>
@@ -5718,7 +5719,7 @@
         <v>0.69630000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>121806</v>
       </c>
@@ -5751,7 +5752,7 @@
         <v>0.69630000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>121807</v>
       </c>
@@ -5794,20 +5795,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC118DC-A31E-40E5-8016-5940C6148308}">
   <dimension ref="A1:K79"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.54296875" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" customWidth="1"/>
-    <col min="9" max="9" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.90625" style="19"/>
+    <col min="1" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>271</v>
       </c>
@@ -5878,7 +5879,7 @@
         <v>0.78339999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>272</v>
       </c>
@@ -5914,7 +5915,7 @@
         <v>0.79090000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>273</v>
       </c>
@@ -5950,7 +5951,7 @@
         <v>0.7893</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -5986,7 +5987,7 @@
         <v>0.78959999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>275</v>
       </c>
@@ -6022,7 +6023,7 @@
         <v>0.78979999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>276</v>
       </c>
@@ -6058,7 +6059,7 @@
         <v>0.77080000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>277</v>
       </c>
@@ -6094,7 +6095,7 @@
         <v>0.78200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>278</v>
       </c>
@@ -6130,7 +6131,7 @@
         <v>0.78349999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>279</v>
       </c>
@@ -6166,7 +6167,7 @@
         <v>0.83450000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>280</v>
       </c>
@@ -6202,7 +6203,7 @@
         <v>0.81469999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>281</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>0.83289999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>282</v>
       </c>
@@ -6274,7 +6275,7 @@
         <v>0.83050000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>283</v>
       </c>
@@ -6310,7 +6311,7 @@
         <v>0.83069999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>299</v>
       </c>
@@ -6346,7 +6347,7 @@
         <v>0.81289999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>300</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>0.81940000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>301</v>
       </c>
@@ -6418,7 +6419,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>302</v>
       </c>
@@ -6454,7 +6455,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>303</v>
       </c>
@@ -6490,7 +6491,7 @@
         <v>0.81840000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>309</v>
       </c>
@@ -6526,7 +6527,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>310</v>
       </c>
@@ -6562,7 +6563,7 @@
         <v>0.82210000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>311</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>0.82330000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>315</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>0.82310000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>316</v>
       </c>
@@ -6670,7 +6671,7 @@
         <v>0.86150000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>319</v>
       </c>
@@ -6706,7 +6707,7 @@
         <v>0.85809999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>320</v>
       </c>
@@ -6742,7 +6743,7 @@
         <v>0.88700000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>321</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>0.88719999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>325</v>
       </c>
@@ -6814,7 +6815,7 @@
         <v>0.87719999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>327</v>
       </c>
@@ -6850,7 +6851,7 @@
         <v>0.86150000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>328</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>0.86629999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>331</v>
       </c>
@@ -6922,7 +6923,7 @@
         <v>0.86529999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -6958,7 +6959,7 @@
         <v>0.86539999999999995</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>334</v>
       </c>
@@ -6994,7 +6995,7 @@
         <v>0.86560000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>336</v>
       </c>
@@ -7030,7 +7031,7 @@
         <v>0.85340000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>337</v>
       </c>
@@ -7066,7 +7067,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>338</v>
       </c>
@@ -7102,7 +7103,7 @@
         <v>0.8649</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>341</v>
       </c>
@@ -7138,7 +7139,7 @@
         <v>0.86480000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>342</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>345</v>
       </c>
@@ -7210,7 +7211,7 @@
         <v>0.87919999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>346</v>
       </c>
@@ -7246,7 +7247,7 @@
         <v>0.90159999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>347</v>
       </c>
@@ -7282,7 +7283,7 @@
         <v>0.90169999999999995</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>351</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>0.8931</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>355</v>
       </c>
@@ -7354,7 +7355,7 @@
         <v>0.8226</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>356</v>
       </c>
@@ -7390,7 +7391,7 @@
         <v>0.82569999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>357</v>
       </c>
@@ -7426,7 +7427,7 @@
         <v>0.82740000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>358</v>
       </c>
@@ -7462,7 +7463,7 @@
         <v>0.83079999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>359</v>
       </c>
@@ -7498,7 +7499,7 @@
         <v>0.83079999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>360</v>
       </c>
@@ -7534,7 +7535,7 @@
         <v>0.83460000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>361</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>0.82279999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>362</v>
       </c>
@@ -7606,7 +7607,7 @@
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>363</v>
       </c>
@@ -7642,7 +7643,7 @@
         <v>0.82340000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>373</v>
       </c>
@@ -7678,7 +7679,7 @@
         <v>0.84460000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>374</v>
       </c>
@@ -7714,7 +7715,7 @@
         <v>0.84730000000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>375</v>
       </c>
@@ -7750,7 +7751,7 @@
         <v>0.8488</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>379</v>
       </c>
@@ -7786,7 +7787,7 @@
         <v>0.8518</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>380</v>
       </c>
@@ -7822,7 +7823,7 @@
         <v>0.8518</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>381</v>
       </c>
@@ -7858,7 +7859,7 @@
         <v>0.85519999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>385</v>
       </c>
@@ -7894,7 +7895,7 @@
         <v>0.8448</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>386</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>0.83950000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>389</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>0.84319999999999995</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>391</v>
       </c>
@@ -8002,7 +8003,7 @@
         <v>0.86380000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>393</v>
       </c>
@@ -8038,7 +8039,7 @@
         <v>0.86609999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>395</v>
       </c>
@@ -8074,7 +8075,7 @@
         <v>0.86739999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>397</v>
       </c>
@@ -8110,7 +8111,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>399</v>
       </c>
@@ -8146,7 +8147,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>401</v>
       </c>
@@ -8182,7 +8183,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>403</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>0.8639</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>405</v>
       </c>
@@ -8254,7 +8255,7 @@
         <v>0.8669</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>407</v>
       </c>
@@ -8290,7 +8291,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>409</v>
       </c>
@@ -8326,7 +8327,7 @@
         <v>0.80420000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>410</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>0.85129999999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>413</v>
       </c>
@@ -8398,7 +8399,7 @@
         <v>0.80420000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>415</v>
       </c>
@@ -8434,7 +8435,7 @@
         <v>0.86970000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>416</v>
       </c>
@@ -8470,7 +8471,7 @@
         <v>0.83460000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>419</v>
       </c>
@@ -8506,7 +8507,7 @@
         <v>0.81640000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>739</v>
       </c>
@@ -8542,7 +8543,7 @@
         <v>0.80530000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>741</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>0.80730000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>743</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>0.82440000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>745</v>
       </c>
@@ -8660,14 +8661,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75CEA00-E98C-48D1-8951-FCFD66D8871D}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.453125" customWidth="1"/>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8687,7 +8688,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>605</v>
       </c>
@@ -8707,7 +8708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>607</v>
       </c>
@@ -8727,7 +8728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>609</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>611</v>
       </c>
@@ -8767,7 +8768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>613</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>614</v>
       </c>
@@ -8807,7 +8808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>615</v>
       </c>
@@ -8827,7 +8828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>617</v>
       </c>
@@ -8847,7 +8848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>619</v>
       </c>
@@ -8867,7 +8868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>621</v>
       </c>
@@ -8887,7 +8888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>623</v>
       </c>
@@ -8907,7 +8908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>624</v>
       </c>
@@ -8927,7 +8928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>625</v>
       </c>
@@ -8947,7 +8948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>627</v>
       </c>
@@ -8967,7 +8968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>629</v>
       </c>
@@ -8987,7 +8988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>631</v>
       </c>
@@ -9015,21 +9016,21 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7291FE-1C80-46D5-A44B-ECDC4D68CA2E}">
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="14" max="14" width="8.90625" style="19"/>
+    <col min="2" max="2" width="57.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9073,7 +9074,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -9118,7 +9119,7 @@
         <v>0.64549999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -9163,7 +9164,7 @@
         <v>0.53690000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -9208,7 +9209,7 @@
         <v>0.7571</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -9298,7 +9299,7 @@
         <v>0.5766</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -9343,7 +9344,7 @@
         <v>0.61140000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -9388,7 +9389,7 @@
         <v>0.73450000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -9433,7 +9434,7 @@
         <v>0.51990000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -9478,7 +9479,7 @@
         <v>0.59840000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>0.63500000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -9568,7 +9569,7 @@
         <v>0.71589999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -9613,7 +9614,7 @@
         <v>0.54020000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -9658,7 +9659,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -9703,7 +9704,7 @@
         <v>0.50380000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -9748,7 +9749,7 @@
         <v>0.72240000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -9793,7 +9794,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -9838,7 +9839,7 @@
         <v>0.53280000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>121</v>
       </c>
@@ -9883,7 +9884,7 @@
         <v>0.60260000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>123</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -9973,7 +9974,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -10018,7 +10019,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -10063,7 +10064,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -10153,7 +10154,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -10198,7 +10199,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>141</v>
       </c>
@@ -10288,7 +10289,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -10333,7 +10334,7 @@
         <v>0.58209999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -10378,7 +10379,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -10423,7 +10424,7 @@
         <v>0.50380000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -10468,7 +10469,7 @@
         <v>0.72240000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -10558,7 +10559,7 @@
         <v>0.53280000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -10603,7 +10604,7 @@
         <v>0.60260000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -10648,7 +10649,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -10693,7 +10694,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -10738,7 +10739,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -10783,7 +10784,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -10828,7 +10829,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -10873,7 +10874,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -10918,7 +10919,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>137</v>
       </c>
@@ -10963,7 +10964,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -11008,7 +11009,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>143</v>
       </c>
@@ -11053,7 +11054,7 @@
         <v>0.58209999999999995</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -11098,7 +11099,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -11143,7 +11144,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -11188,7 +11189,7 @@
         <v>0.73450000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -11233,7 +11234,7 @@
         <v>0.54020000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>129</v>
       </c>
@@ -11278,7 +11279,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -11368,7 +11369,7 @@
         <v>0.54630000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -11413,7 +11414,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>145</v>
       </c>
@@ -11468,16 +11469,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E191415-7327-4CFF-B229-D7F54ABBDB32}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" customWidth="1"/>
-    <col min="6" max="6" width="8.90625" style="19"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>169</v>
       </c>
@@ -11526,15 +11527,15 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25522428-B4D4-43A2-8ABC-2052B8318014}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="30.54296875" customWidth="1"/>
-    <col min="6" max="6" width="8.90625" style="19"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="30.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11554,7 +11555,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>167</v>
       </c>
@@ -11583,17 +11584,17 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A5EDD5-EC5E-4B4D-BAE8-EF24A4D32E1E}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" customWidth="1"/>
-    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.90625" style="19"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11613,7 +11614,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -11642,15 +11643,15 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C72381-812D-42EC-84BC-3CAA921F011E}">
   <dimension ref="A1:G93"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11673,7 +11674,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>425</v>
       </c>
@@ -11696,7 +11697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>427</v>
       </c>
@@ -11719,7 +11720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>429</v>
       </c>
@@ -11742,7 +11743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>430</v>
       </c>
@@ -11765,7 +11766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>431</v>
       </c>
@@ -11788,7 +11789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>432</v>
       </c>
@@ -11811,7 +11812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>433</v>
       </c>
@@ -11834,7 +11835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>434</v>
       </c>
@@ -11857,7 +11858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>435</v>
       </c>
@@ -11880,7 +11881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>436</v>
       </c>
@@ -11903,7 +11904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>445</v>
       </c>
@@ -11926,7 +11927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>446</v>
       </c>
@@ -11949,7 +11950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -11972,7 +11973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>448</v>
       </c>
@@ -11995,7 +11996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>449</v>
       </c>
@@ -12018,7 +12019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>450</v>
       </c>
@@ -12041,7 +12042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>457</v>
       </c>
@@ -12064,7 +12065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>459</v>
       </c>
@@ -12087,7 +12088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>461</v>
       </c>
@@ -12110,7 +12111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>463</v>
       </c>
@@ -12133,7 +12134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>464</v>
       </c>
@@ -12156,7 +12157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>467</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>468</v>
       </c>
@@ -12202,7 +12203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>469</v>
       </c>
@@ -12225,7 +12226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>473</v>
       </c>
@@ -12248,7 +12249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>475</v>
       </c>
@@ -12271,7 +12272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>477</v>
       </c>
@@ -12294,7 +12295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>479</v>
       </c>
@@ -12317,7 +12318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>480</v>
       </c>
@@ -12340,7 +12341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>483</v>
       </c>
@@ -12363,7 +12364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>485</v>
       </c>
@@ -12386,7 +12387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>487</v>
       </c>
@@ -12409,7 +12410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>488</v>
       </c>
@@ -12432,7 +12433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>491</v>
       </c>
@@ -12455,7 +12456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>493</v>
       </c>
@@ -12478,7 +12479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>494</v>
       </c>
@@ -12501,7 +12502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>495</v>
       </c>
@@ -12524,7 +12525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>496</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>497</v>
       </c>
@@ -12570,7 +12571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>498</v>
       </c>
@@ -12593,7 +12594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>499</v>
       </c>
@@ -12616,7 +12617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>507</v>
       </c>
@@ -12639,7 +12640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>509</v>
       </c>
@@ -12662,7 +12663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>511</v>
       </c>
@@ -12685,7 +12686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>513</v>
       </c>
@@ -12708,7 +12709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>515</v>
       </c>
@@ -12731,7 +12732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>516</v>
       </c>
@@ -12754,7 +12755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>517</v>
       </c>
@@ -12777,7 +12778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>518</v>
       </c>
@@ -12800,7 +12801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>519</v>
       </c>
@@ -12823,7 +12824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>525</v>
       </c>
@@ -12846,7 +12847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>526</v>
       </c>
@@ -12869,7 +12870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>529</v>
       </c>
@@ -12892,7 +12893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>531</v>
       </c>
@@ -12915,7 +12916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>532</v>
       </c>
@@ -12938,7 +12939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>533</v>
       </c>
@@ -12961,7 +12962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>535</v>
       </c>
@@ -12984,7 +12985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>537</v>
       </c>
@@ -13007,7 +13008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>539</v>
       </c>
@@ -13030,7 +13031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>541</v>
       </c>
@@ -13053,7 +13054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>543</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>544</v>
       </c>
@@ -13099,7 +13100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>545</v>
       </c>
@@ -13122,7 +13123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>546</v>
       </c>
@@ -13145,7 +13146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>551</v>
       </c>
@@ -13168,7 +13169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>553</v>
       </c>
@@ -13191,7 +13192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>555</v>
       </c>
@@ -13214,7 +13215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>557</v>
       </c>
@@ -13237,7 +13238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>558</v>
       </c>
@@ -13260,7 +13261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>559</v>
       </c>
@@ -13283,7 +13284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>560</v>
       </c>
@@ -13306,7 +13307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>563</v>
       </c>
@@ -13329,7 +13330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>564</v>
       </c>
@@ -13352,7 +13353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>565</v>
       </c>
@@ -13375,7 +13376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>566</v>
       </c>
@@ -13398,7 +13399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>567</v>
       </c>
@@ -13421,7 +13422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>573</v>
       </c>
@@ -13444,7 +13445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>575</v>
       </c>
@@ -13467,7 +13468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>576</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>577</v>
       </c>
@@ -13513,7 +13514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -13536,7 +13537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>583</v>
       </c>
@@ -13559,7 +13560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>585</v>
       </c>
@@ -13582,7 +13583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>587</v>
       </c>
@@ -13605,7 +13606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>589</v>
       </c>
@@ -13628,7 +13629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>591</v>
       </c>
@@ -13651,7 +13652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>593</v>
       </c>
@@ -13674,7 +13675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>595</v>
       </c>
@@ -13697,7 +13698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>597</v>
       </c>
@@ -13720,7 +13721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>599</v>
       </c>
@@ -13743,7 +13744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>600</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>601</v>
       </c>
@@ -13799,19 +13800,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0952EC0-78E2-4227-94D1-113308784769}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="8.90625" style="19"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -13840,7 +13841,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -13870,7 +13871,7 @@
         <v>0.50009999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -13900,7 +13901,7 @@
         <v>0.5181</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -13930,7 +13931,7 @@
         <v>0.51949999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -13960,7 +13961,7 @@
         <v>0.59840000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -13990,7 +13991,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -14020,7 +14021,7 @@
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -14058,17 +14059,17 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE280E8-1030-4D15-BB87-39545B71D8FE}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="19"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14091,7 +14092,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -14115,7 +14116,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -14147,15 +14148,15 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC3D159-7610-47A2-B6E6-4BC8DBFBC056}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14175,7 +14176,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>633</v>
       </c>
@@ -14195,7 +14196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>635</v>
       </c>
@@ -14215,7 +14216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>637</v>
       </c>
@@ -14235,7 +14236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>639</v>
       </c>
@@ -14255,7 +14256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>641</v>
       </c>
@@ -14275,7 +14276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>643</v>
       </c>
@@ -14295,7 +14296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>645</v>
       </c>
@@ -14315,7 +14316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>647</v>
       </c>
@@ -14335,7 +14336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>649</v>
       </c>
@@ -14355,7 +14356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>651</v>
       </c>
@@ -14375,7 +14376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>653</v>
       </c>
@@ -14395,7 +14396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>655</v>
       </c>
@@ -14415,7 +14416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>657</v>
       </c>
@@ -14435,7 +14436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>659</v>
       </c>
@@ -14455,7 +14456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>660</v>
       </c>
@@ -14483,14 +14484,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA1586A9-3200-4887-94DE-CCF39E21CB1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="73.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="22" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14501,7 +14502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>750</v>
       </c>
@@ -14512,7 +14513,7 @@
         <v>8841</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>752</v>
       </c>
@@ -14523,7 +14524,7 @@
         <v>12406</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>754</v>
       </c>
@@ -14534,7 +14535,7 @@
         <v>9150</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>755</v>
       </c>
@@ -14551,17 +14552,26 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3ECFA3-9985-4F85-AADB-8BFBCABD9887}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D45C86-8F36-4726-BB8C-72524168E246}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14581,7 +14591,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>662</v>
       </c>
@@ -14601,7 +14611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>664</v>
       </c>
@@ -14621,7 +14631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>666</v>
       </c>
@@ -14641,7 +14651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>668</v>
       </c>
@@ -14661,7 +14671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>670</v>
       </c>
@@ -14681,7 +14691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>672</v>
       </c>
@@ -14701,7 +14711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>674</v>
       </c>
@@ -14721,7 +14731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>675</v>
       </c>
@@ -14741,7 +14751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>677</v>
       </c>
@@ -14770,16 +14780,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C460FD-853F-48A8-BB18-DB58CBD5BD31}">
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -14796,7 +14806,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -14814,7 +14824,7 @@
         <v>0.53449999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -14832,7 +14842,7 @@
         <v>0.50009999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -14850,7 +14860,7 @@
         <v>0.5181</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -14868,7 +14878,7 @@
         <v>0.56310000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -14886,7 +14896,7 @@
         <v>0.69259999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -14904,7 +14914,7 @@
         <v>0.58479999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -14922,7 +14932,7 @@
         <v>0.52429999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -14940,7 +14950,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -14958,7 +14968,7 @@
         <v>0.51949999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -14976,7 +14986,7 @@
         <v>0.59850000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -14994,7 +15004,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -15012,7 +15022,7 @@
         <v>0.61990000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -15030,7 +15040,7 @@
         <v>0.64549999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -15048,7 +15058,7 @@
         <v>0.53690000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -15066,7 +15076,7 @@
         <v>0.75700000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -15084,7 +15094,7 @@
         <v>0.56530000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -15102,7 +15112,7 @@
         <v>0.5766</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -15120,7 +15130,7 @@
         <v>0.61140000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -15138,7 +15148,7 @@
         <v>0.73440000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -15156,7 +15166,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -15174,7 +15184,7 @@
         <v>0.59860000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -15192,7 +15202,7 @@
         <v>0.6351</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -15210,7 +15220,7 @@
         <v>0.71599999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -15228,7 +15238,7 @@
         <v>0.5403</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -15246,7 +15256,7 @@
         <v>0.54359999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -15264,7 +15274,7 @@
         <v>0.79559999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -15282,7 +15292,7 @@
         <v>0.73480000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -15300,7 +15310,7 @@
         <v>0.71530000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -15318,7 +15328,7 @@
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -15336,7 +15346,7 @@
         <v>0.64339999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -15354,7 +15364,7 @@
         <v>0.6109</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -15372,7 +15382,7 @@
         <v>0.62250000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -15390,7 +15400,7 @@
         <v>0.54469999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -15408,7 +15418,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -15426,7 +15436,7 @@
         <v>0.58220000000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -15444,7 +15454,7 @@
         <v>0.51819999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -15462,7 +15472,7 @@
         <v>0.27089999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -15480,7 +15490,7 @@
         <v>0.57320000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -15498,7 +15508,7 @@
         <v>0.58879999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -15516,7 +15526,7 @@
         <v>0.48780000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -15534,7 +15544,7 @@
         <v>0.5796</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -15552,7 +15562,7 @@
         <v>0.57920000000000005</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -15570,7 +15580,7 @@
         <v>0.60460000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -15588,7 +15598,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -15606,7 +15616,7 @@
         <v>0.65529999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -15624,7 +15634,7 @@
         <v>0.53590000000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -15642,7 +15652,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -15660,7 +15670,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -15678,7 +15688,7 @@
         <v>0.58109999999999995</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>81</v>
       </c>
@@ -15696,7 +15706,7 @@
         <v>0.48780000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -15714,7 +15724,7 @@
         <v>0.5796</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>101</v>
       </c>
@@ -15732,7 +15742,7 @@
         <v>0.60860000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -15750,7 +15760,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -15768,7 +15778,7 @@
         <v>0.58260000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -15786,7 +15796,7 @@
         <v>0.59009999999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -15804,7 +15814,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>109</v>
       </c>
@@ -15822,7 +15832,7 @@
         <v>0.70830000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -15840,7 +15850,7 @@
         <v>0.64939999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -15858,7 +15868,7 @@
         <v>0.50370000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -15876,7 +15886,7 @@
         <v>0.72250000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -15894,7 +15904,7 @@
         <v>0.73460000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -15912,7 +15922,7 @@
         <v>0.53269999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -15930,7 +15940,7 @@
         <v>0.60270000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>123</v>
       </c>
@@ -15948,7 +15958,7 @@
         <v>0.59940000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>125</v>
       </c>
@@ -15966,7 +15976,7 @@
         <v>0.56030000000000002</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -15984,7 +15994,7 @@
         <v>0.73409999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -16002,7 +16012,7 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>131</v>
       </c>
@@ -16020,7 +16030,7 @@
         <v>0.63219999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>133</v>
       </c>
@@ -16038,7 +16048,7 @@
         <v>0.68679999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>135</v>
       </c>
@@ -16056,7 +16066,7 @@
         <v>0.55689999999999995</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>137</v>
       </c>
@@ -16074,7 +16084,7 @@
         <v>0.55130000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>139</v>
       </c>
@@ -16092,7 +16102,7 @@
         <v>0.67789999999999995</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>141</v>
       </c>
@@ -16110,7 +16120,7 @@
         <v>0.68840000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>143</v>
       </c>
@@ -16128,7 +16138,7 @@
         <v>0.58220000000000005</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>145</v>
       </c>
@@ -16146,7 +16156,7 @@
         <v>0.57440000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>147</v>
       </c>
@@ -16164,7 +16174,7 @@
         <v>0.53210000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>149</v>
       </c>
@@ -16182,7 +16192,7 @@
         <v>0.4556</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>151</v>
       </c>
@@ -16200,7 +16210,7 @@
         <v>0.52790000000000004</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>153</v>
       </c>
@@ -16218,7 +16228,7 @@
         <v>0.53380000000000005</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -16236,7 +16246,7 @@
         <v>0.59209999999999996</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>157</v>
       </c>
@@ -16254,7 +16264,7 @@
         <v>0.48980000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -16272,7 +16282,7 @@
         <v>0.70179999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>161</v>
       </c>
@@ -16290,7 +16300,7 @@
         <v>0.49159999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -16308,7 +16318,7 @@
         <v>0.49249999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -16326,7 +16336,7 @@
         <v>0.64149999999999996</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -16344,7 +16354,7 @@
         <v>0.87329999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>169</v>
       </c>
@@ -16362,7 +16372,7 @@
         <v>0.64270000000000005</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>171</v>
       </c>
@@ -16380,7 +16390,7 @@
         <v>0.68020000000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>173</v>
       </c>
@@ -16398,7 +16408,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>175</v>
       </c>
@@ -16416,7 +16426,7 @@
         <v>0.64359999999999995</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>177</v>
       </c>
@@ -16434,7 +16444,7 @@
         <v>0.66600000000000004</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>179</v>
       </c>
@@ -16452,7 +16462,7 @@
         <v>0.65149999999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>181</v>
       </c>
@@ -16480,15 +16490,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EC6327-8CBD-476A-BB08-5C75376F1333}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" style="19"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -16505,7 +16515,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -16523,7 +16533,7 @@
         <v>0.49159999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -16549,17 +16559,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF069F-11F0-41FB-B939-51B5F45B8CB2}">
   <dimension ref="A1:G111"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="13" style="17" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="19"/>
+    <col min="6" max="6" width="12.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -16582,7 +16592,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>689</v>
       </c>
@@ -16607,7 +16617,7 @@
         <v>0.71970000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>690</v>
       </c>
@@ -16632,7 +16642,7 @@
         <v>0.63970000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>691</v>
       </c>
@@ -16657,7 +16667,7 @@
         <v>0.66990000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>692</v>
       </c>
@@ -16682,7 +16692,7 @@
         <v>0.70860000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>693</v>
       </c>
@@ -16707,7 +16717,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>694</v>
       </c>
@@ -16732,7 +16742,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>696</v>
       </c>
@@ -16757,7 +16767,7 @@
         <v>0.72819999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>697</v>
       </c>
@@ -16782,7 +16792,7 @@
         <v>0.65349999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>698</v>
       </c>
@@ -16807,7 +16817,7 @@
         <v>0.67920000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>699</v>
       </c>
@@ -16832,7 +16842,7 @@
         <v>0.71709999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>700</v>
       </c>
@@ -16857,7 +16867,7 @@
         <v>0.60129999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>701</v>
       </c>
@@ -16882,7 +16892,7 @@
         <v>0.6038</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>702</v>
       </c>
@@ -16907,679 +16917,679 @@
         <v>0.2114</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="27"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="27"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="27"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="27"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="27"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="27"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="27"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="27"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="27"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="27"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="27"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="27"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="27"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="27"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="27"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="27"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="27"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="27"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="27"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="27"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="27"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="27"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="27"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="27"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="27"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="27"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="27"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="27"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="27"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="E49" s="27"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
       <c r="E50" s="27"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
       <c r="E51" s="27"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
       <c r="E52" s="27"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="27"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="27"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
       <c r="E55" s="27"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
       <c r="E56" s="27"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="27"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
       <c r="E58" s="27"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
       <c r="E59" s="27"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
       <c r="E60" s="27"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
       <c r="E61" s="27"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
       <c r="E62" s="27"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
       <c r="E63" s="27"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
       <c r="E64" s="27"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
       <c r="E65" s="27"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
       <c r="E66" s="27"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
       <c r="E67" s="27"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
       <c r="E68" s="27"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
       <c r="E69" s="27"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
       <c r="E70" s="27"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
       <c r="E71" s="27"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="11"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
       <c r="E72" s="27"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
       <c r="E73" s="27"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="11"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
       <c r="E74" s="27"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
       <c r="E75" s="27"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="11"/>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
       <c r="E76" s="27"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
       <c r="E77" s="27"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
       <c r="E78" s="27"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="11"/>
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="27"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
       <c r="E80" s="27"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="11"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
       <c r="E81" s="27"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="11"/>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
       <c r="E82" s="27"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
       <c r="E83" s="27"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
       <c r="E84" s="27"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
       <c r="E85" s="27"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
       <c r="E86" s="27"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="11"/>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
       <c r="E87" s="27"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
       <c r="E88" s="27"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
       <c r="E89" s="27"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="11"/>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
       <c r="E90" s="27"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="11"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
       <c r="E91" s="27"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="11"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
       <c r="E92" s="27"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
       <c r="E93" s="27"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
       <c r="E94" s="27"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="11"/>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
       <c r="E95" s="27"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="11"/>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
       <c r="E96" s="27"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
       <c r="E97" s="27"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="11"/>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
       <c r="E98" s="27"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="11"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
       <c r="E99" s="27"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="11"/>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="27"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="11"/>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="27"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="27"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="11"/>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="27"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="11"/>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="27"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="11"/>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
       <c r="E105" s="27"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="11"/>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
       <c r="E106" s="27"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
       <c r="E107" s="27"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="11"/>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
       <c r="E108" s="27"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="11"/>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
       <c r="E109" s="27"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="11"/>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
       <c r="E110" s="27"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="11"/>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
@@ -17594,17 +17604,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E21284-68D2-4B7C-8891-F33FB2D4174C}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
     <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="19"/>
+    <col min="8" max="8" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17630,7 +17640,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -17657,7 +17667,7 @@
         <v>0.54469999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -17684,7 +17694,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -17711,7 +17721,7 @@
         <v>0.58230000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -17738,7 +17748,7 @@
         <v>0.51819999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -17765,7 +17775,7 @@
         <v>0.4879</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -17800,16 +17810,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7C1833-5DC7-4038-9B0D-2D47C7DFB4A9}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="6" max="6" width="8.90625" style="19"/>
+    <col min="6" max="6" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17829,7 +17839,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -17850,7 +17860,7 @@
         <v>0.56310000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -17879,18 +17889,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6578FDA-80BC-4521-8BA7-3C8BD0257781}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="19"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17916,7 +17926,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -17943,7 +17953,7 @@
         <v>0.60460000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -17970,7 +17980,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -17997,7 +18007,7 @@
         <v>0.65529999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -18024,7 +18034,7 @@
         <v>0.53590000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -18051,7 +18061,7 @@
         <v>0.4879</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -18086,17 +18096,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC341ECE-6FE5-41E4-9F6E-2DB5B33BB710}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="19"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -18119,7 +18129,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -18143,7 +18153,7 @@
         <v>0.60860000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -18167,7 +18177,7 @@
         <v>0.5827</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -18191,7 +18201,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>107</v>
       </c>
